--- a/research/traditional_assets/database/data/jamaica/jamaica_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_restaurant_dining.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1331269383444697</v>
+        <v>0.1328278709986085</v>
       </c>
       <c r="C2">
-        <v>83.42387892238844</v>
+        <v>82.9212485949579</v>
       </c>
       <c r="D2">
-        <v>83.33287892238845</v>
+        <v>83.61924859495791</v>
       </c>
       <c r="E2">
-        <v>-43.2</v>
+        <v>-42.411</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.789</v>
       </c>
       <c r="G2">
         <v>0.091</v>
@@ -1451,28 +1451,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0396867</v>
       </c>
       <c r="N2">
-        <v>4.783333333333333</v>
+        <v>4.743646633333333</v>
       </c>
       <c r="O2">
-        <v>1.195833333333333</v>
+        <v>1.185911658333333</v>
       </c>
       <c r="P2">
-        <v>3.5875</v>
+        <v>3.557734975</v>
       </c>
       <c r="Q2">
-        <v>7.0175</v>
+        <v>6.987734975</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1331269383444697</v>
+        <v>0.1337885060592006</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326222</v>
+        <v>0.850916101658627</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>120.5273639111676</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1328278709986085</v>
+        <v>0.1325288036527474</v>
       </c>
       <c r="C3">
-        <v>82.9212485949579</v>
+        <v>82.42059324733346</v>
       </c>
       <c r="D3">
-        <v>83.61924859495791</v>
+        <v>83.90759324733347</v>
       </c>
       <c r="E3">
-        <v>-42.411</v>
+        <v>-41.622</v>
       </c>
       <c r="F3">
-        <v>0.789</v>
+        <v>1.578</v>
       </c>
       <c r="G3">
         <v>0.091</v>
@@ -1533,28 +1533,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M3">
-        <v>0.0396867</v>
+        <v>0.0793734</v>
       </c>
       <c r="N3">
-        <v>4.743646633333333</v>
+        <v>4.703959933333334</v>
       </c>
       <c r="O3">
-        <v>1.185911658333333</v>
+        <v>1.175989983333333</v>
       </c>
       <c r="P3">
-        <v>3.557734975</v>
+        <v>3.52796995</v>
       </c>
       <c r="Q3">
-        <v>6.987734975</v>
+        <v>6.957969950000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1337885060592006</v>
+        <v>0.1344635751558647</v>
       </c>
       <c r="T3">
-        <v>0.850916101658627</v>
+        <v>0.8574445357667951</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>120.5273639111676</v>
+        <v>60.26368195558378</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1325288036527474</v>
+        <v>0.1322297363068862</v>
       </c>
       <c r="C4">
-        <v>82.42059324733346</v>
+        <v>81.92193338120796</v>
       </c>
       <c r="D4">
-        <v>83.90759324733347</v>
+        <v>84.19793338120797</v>
       </c>
       <c r="E4">
-        <v>-41.622</v>
+        <v>-40.83300000000001</v>
       </c>
       <c r="F4">
-        <v>1.578</v>
+        <v>2.367</v>
       </c>
       <c r="G4">
         <v>0.091</v>
@@ -1615,28 +1615,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M4">
-        <v>0.0793734</v>
+        <v>0.1190601</v>
       </c>
       <c r="N4">
-        <v>4.703959933333334</v>
+        <v>4.664273233333334</v>
       </c>
       <c r="O4">
-        <v>1.175989983333333</v>
+        <v>1.166068308333333</v>
       </c>
       <c r="P4">
-        <v>3.52796995</v>
+        <v>3.498204925</v>
       </c>
       <c r="Q4">
-        <v>6.957969950000001</v>
+        <v>6.928204925000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1344635751558647</v>
+        <v>0.1351525632029755</v>
       </c>
       <c r="T4">
-        <v>0.8574445357667951</v>
+        <v>0.8641075767637912</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.26368195558378</v>
+        <v>40.17578797038919</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1322297363068862</v>
+        <v>0.1319306689610251</v>
       </c>
       <c r="C5">
-        <v>81.92193338120796</v>
+        <v>81.42528978302235</v>
       </c>
       <c r="D5">
-        <v>84.19793338120797</v>
+        <v>84.49028978302236</v>
       </c>
       <c r="E5">
-        <v>-40.83300000000001</v>
+        <v>-40.044</v>
       </c>
       <c r="F5">
-        <v>2.367</v>
+        <v>3.156</v>
       </c>
       <c r="G5">
         <v>0.091</v>
@@ -1697,28 +1697,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M5">
-        <v>0.1190601</v>
+        <v>0.1587468</v>
       </c>
       <c r="N5">
-        <v>4.664273233333334</v>
+        <v>4.624586533333333</v>
       </c>
       <c r="O5">
-        <v>1.166068308333333</v>
+        <v>1.156146633333333</v>
       </c>
       <c r="P5">
-        <v>3.498204925</v>
+        <v>3.4684399</v>
       </c>
       <c r="Q5">
-        <v>6.928204925000001</v>
+        <v>6.8984399</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1351525632029755</v>
+        <v>0.1358559051677344</v>
       </c>
       <c r="T5">
-        <v>0.8641075767637912</v>
+        <v>0.8709094311148917</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.17578797038919</v>
+        <v>30.13184097779189</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1319306689610251</v>
+        <v>0.1316316016151639</v>
       </c>
       <c r="C6">
-        <v>81.42528978302235</v>
+        <v>80.93068352892664</v>
       </c>
       <c r="D6">
-        <v>84.49028978302236</v>
+        <v>84.78468352892665</v>
       </c>
       <c r="E6">
-        <v>-40.044</v>
+        <v>-39.255</v>
       </c>
       <c r="F6">
-        <v>3.156</v>
+        <v>3.945</v>
       </c>
       <c r="G6">
         <v>0.091</v>
@@ -1779,28 +1779,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M6">
-        <v>0.1587468</v>
+        <v>0.1984335</v>
       </c>
       <c r="N6">
-        <v>4.624586533333333</v>
+        <v>4.584899833333333</v>
       </c>
       <c r="O6">
-        <v>1.156146633333333</v>
+        <v>1.146224958333333</v>
       </c>
       <c r="P6">
-        <v>3.4684399</v>
+        <v>3.438674875</v>
       </c>
       <c r="Q6">
-        <v>6.8984399</v>
+        <v>6.868674875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1358559051677344</v>
+        <v>0.1365740543317514</v>
       </c>
       <c r="T6">
-        <v>0.8709094311148917</v>
+        <v>0.8778544823996994</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.13184097779189</v>
+        <v>24.10547278223351</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1316316016151639</v>
+        <v>0.1313325342693027</v>
       </c>
       <c r="C7">
-        <v>80.93068352892664</v>
+        <v>80.43813598984448</v>
       </c>
       <c r="D7">
-        <v>84.78468352892665</v>
+        <v>85.08113598984448</v>
       </c>
       <c r="E7">
-        <v>-39.255</v>
+        <v>-38.466</v>
       </c>
       <c r="F7">
-        <v>3.945</v>
+        <v>4.734000000000001</v>
       </c>
       <c r="G7">
         <v>0.091</v>
@@ -1861,28 +1861,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M7">
-        <v>0.1984335</v>
+        <v>0.2381202</v>
       </c>
       <c r="N7">
-        <v>4.584899833333333</v>
+        <v>4.545213133333333</v>
       </c>
       <c r="O7">
-        <v>1.146224958333333</v>
+        <v>1.136303283333333</v>
       </c>
       <c r="P7">
-        <v>3.438674875</v>
+        <v>3.40890985</v>
       </c>
       <c r="Q7">
-        <v>6.868674875</v>
+        <v>6.83890985</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1365740543317514</v>
+        <v>0.1373074832652156</v>
       </c>
       <c r="T7">
-        <v>0.8778544823996994</v>
+        <v>0.8849473007331201</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.10547278223351</v>
+        <v>20.08789398519459</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1313325342693027</v>
+        <v>0.1310334669234415</v>
       </c>
       <c r="C8">
-        <v>80.43813598984448</v>
+        <v>79.94766883664504</v>
       </c>
       <c r="D8">
-        <v>85.08113598984448</v>
+        <v>85.37966883664504</v>
       </c>
       <c r="E8">
-        <v>-38.466</v>
+        <v>-37.67700000000001</v>
       </c>
       <c r="F8">
-        <v>4.734</v>
+        <v>5.523</v>
       </c>
       <c r="G8">
         <v>0.091</v>
@@ -1943,28 +1943,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M8">
-        <v>0.2381202</v>
+        <v>0.2778069</v>
       </c>
       <c r="N8">
-        <v>4.545213133333333</v>
+        <v>4.505526433333333</v>
       </c>
       <c r="O8">
-        <v>1.136303283333333</v>
+        <v>1.126381608333333</v>
       </c>
       <c r="P8">
-        <v>3.40890985</v>
+        <v>3.379144825</v>
       </c>
       <c r="Q8">
-        <v>6.83890985</v>
+        <v>6.809144825000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1373074832652156</v>
+        <v>0.1380566848639156</v>
       </c>
       <c r="T8">
-        <v>0.8849473007331201</v>
+        <v>0.8921926527941412</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.08789398519459</v>
+        <v>17.21819484445251</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1310334669234415</v>
+        <v>0.1307343995775803</v>
       </c>
       <c r="C9">
-        <v>79.94766883664505</v>
+        <v>79.45930404542352</v>
       </c>
       <c r="D9">
-        <v>85.37966883664505</v>
+        <v>85.68030404542353</v>
       </c>
       <c r="E9">
-        <v>-37.677</v>
+        <v>-36.88800000000001</v>
       </c>
       <c r="F9">
-        <v>5.523000000000001</v>
+        <v>6.312</v>
       </c>
       <c r="G9">
         <v>0.091</v>
@@ -2025,28 +2025,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M9">
-        <v>0.2778069</v>
+        <v>0.3174936</v>
       </c>
       <c r="N9">
-        <v>4.505526433333333</v>
+        <v>4.465839733333334</v>
       </c>
       <c r="O9">
-        <v>1.126381608333333</v>
+        <v>1.116459933333333</v>
       </c>
       <c r="P9">
-        <v>3.379144825</v>
+        <v>3.3493798</v>
       </c>
       <c r="Q9">
-        <v>6.809144825000001</v>
+        <v>6.779379800000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1380566848639156</v>
+        <v>0.1388221734538917</v>
       </c>
       <c r="T9">
-        <v>0.8921926527941412</v>
+        <v>0.8995955125086629</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.2181948444525</v>
+        <v>15.06592048889595</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1307343995775803</v>
+        <v>0.1304353322317192</v>
       </c>
       <c r="C10">
-        <v>79.45930404542352</v>
+        <v>78.97306390289404</v>
       </c>
       <c r="D10">
-        <v>85.68030404542353</v>
+        <v>85.98306390289405</v>
       </c>
       <c r="E10">
-        <v>-36.88800000000001</v>
+        <v>-36.099</v>
       </c>
       <c r="F10">
-        <v>6.312</v>
+        <v>7.101</v>
       </c>
       <c r="G10">
         <v>0.091</v>
@@ -2107,28 +2107,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M10">
-        <v>0.3174936</v>
+        <v>0.3571803</v>
       </c>
       <c r="N10">
-        <v>4.465839733333334</v>
+        <v>4.426153033333334</v>
       </c>
       <c r="O10">
-        <v>1.116459933333333</v>
+        <v>1.106538258333333</v>
       </c>
       <c r="P10">
-        <v>3.3493798</v>
+        <v>3.319614775</v>
       </c>
       <c r="Q10">
-        <v>6.779379800000001</v>
+        <v>6.749614775</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1388221734538917</v>
+        <v>0.1396044859689222</v>
       </c>
       <c r="T10">
-        <v>0.8995955125086629</v>
+        <v>0.9071610724366903</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.06592048889595</v>
+        <v>13.39192932346306</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1304353322317192</v>
+        <v>0.130248764885858</v>
       </c>
       <c r="C11">
-        <v>78.97306390289404</v>
+        <v>78.37402087909204</v>
       </c>
       <c r="D11">
-        <v>85.98306390289405</v>
+        <v>86.17302087909205</v>
       </c>
       <c r="E11">
-        <v>-36.099</v>
+        <v>-35.31</v>
       </c>
       <c r="F11">
-        <v>7.101</v>
+        <v>7.89</v>
       </c>
       <c r="G11">
         <v>0.091</v>
@@ -2189,45 +2189,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M11">
-        <v>0.3571803</v>
+        <v>0.408702</v>
       </c>
       <c r="N11">
-        <v>4.426153033333334</v>
+        <v>4.374631333333333</v>
       </c>
       <c r="O11">
-        <v>1.106538258333333</v>
+        <v>1.093657833333333</v>
       </c>
       <c r="P11">
-        <v>3.319614775</v>
+        <v>3.2809735</v>
       </c>
       <c r="Q11">
-        <v>6.749614775</v>
+        <v>6.7109735</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1396044859689222</v>
+        <v>0.1404041832065089</v>
       </c>
       <c r="T11">
-        <v>0.9071610724366903</v>
+        <v>0.914894755918674</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.39192932346306</v>
+        <v>11.70371892805353</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.130248764885858</v>
+        <v>0.1299609475399968</v>
       </c>
       <c r="C12">
-        <v>78.37402087909204</v>
+        <v>77.87971920271147</v>
       </c>
       <c r="D12">
-        <v>86.17302087909205</v>
+        <v>86.46771920271148</v>
       </c>
       <c r="E12">
-        <v>-35.31</v>
+        <v>-34.521</v>
       </c>
       <c r="F12">
-        <v>7.890000000000001</v>
+        <v>8.679</v>
       </c>
       <c r="G12">
         <v>0.091</v>
@@ -2271,28 +2271,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M12">
-        <v>0.408702</v>
+        <v>0.4495722</v>
       </c>
       <c r="N12">
-        <v>4.374631333333333</v>
+        <v>4.333761133333333</v>
       </c>
       <c r="O12">
-        <v>1.093657833333333</v>
+        <v>1.083440283333333</v>
       </c>
       <c r="P12">
-        <v>3.2809735</v>
+        <v>3.25032085</v>
       </c>
       <c r="Q12">
-        <v>6.7109735</v>
+        <v>6.680320849999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1404041832065089</v>
+        <v>0.1412218511685358</v>
       </c>
       <c r="T12">
-        <v>0.914894755918674</v>
+        <v>0.9228022300407024</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.70371892805353</v>
+        <v>10.63974448004866</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1299609475399968</v>
+        <v>0.1298261301941356</v>
       </c>
       <c r="C13">
-        <v>77.87971920271147</v>
+        <v>77.22945400316755</v>
       </c>
       <c r="D13">
-        <v>86.46771920271148</v>
+        <v>86.60645400316756</v>
       </c>
       <c r="E13">
-        <v>-34.521</v>
+        <v>-33.732</v>
       </c>
       <c r="F13">
-        <v>8.679</v>
+        <v>9.468</v>
       </c>
       <c r="G13">
         <v>0.091</v>
@@ -2353,45 +2353,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M13">
-        <v>0.4495722</v>
+        <v>0.506538</v>
       </c>
       <c r="N13">
-        <v>4.333761133333333</v>
+        <v>4.276795333333333</v>
       </c>
       <c r="O13">
-        <v>1.083440283333333</v>
+        <v>1.069198833333333</v>
       </c>
       <c r="P13">
-        <v>3.25032085</v>
+        <v>3.2075965</v>
       </c>
       <c r="Q13">
-        <v>6.680320849999999</v>
+        <v>6.637596500000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1412218511685358</v>
+        <v>0.142058102493336</v>
       </c>
       <c r="T13">
-        <v>0.9228022300407024</v>
+        <v>0.9308894194836859</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.63974448004866</v>
+        <v>9.443187546311101</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1298261301941356</v>
+        <v>0.1295510628482745</v>
       </c>
       <c r="C14">
-        <v>77.22945400316755</v>
+        <v>76.72489943737362</v>
       </c>
       <c r="D14">
-        <v>86.60645400316756</v>
+        <v>86.89089943737363</v>
       </c>
       <c r="E14">
-        <v>-33.732</v>
+        <v>-32.943</v>
       </c>
       <c r="F14">
-        <v>9.468</v>
+        <v>10.257</v>
       </c>
       <c r="G14">
         <v>0.091</v>
@@ -2435,28 +2435,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M14">
-        <v>0.506538</v>
+        <v>0.5487495000000001</v>
       </c>
       <c r="N14">
-        <v>4.276795333333333</v>
+        <v>4.234583833333333</v>
       </c>
       <c r="O14">
-        <v>1.069198833333333</v>
+        <v>1.058645958333333</v>
       </c>
       <c r="P14">
-        <v>3.2075965</v>
+        <v>3.175937875</v>
       </c>
       <c r="Q14">
-        <v>6.637596500000001</v>
+        <v>6.605937875</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.142058102493336</v>
+        <v>0.1429135779865224</v>
       </c>
       <c r="T14">
-        <v>0.9308894194836859</v>
+        <v>0.9391625213276574</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.443187546311101</v>
+        <v>8.71678850428717</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1295510628482745</v>
+        <v>0.1292759955024133</v>
       </c>
       <c r="C15">
-        <v>76.72489943737362</v>
+        <v>76.2222194619972</v>
       </c>
       <c r="D15">
-        <v>86.89089943737363</v>
+        <v>87.17721946199721</v>
       </c>
       <c r="E15">
-        <v>-32.943</v>
+        <v>-32.154</v>
       </c>
       <c r="F15">
-        <v>10.257</v>
+        <v>11.046</v>
       </c>
       <c r="G15">
         <v>0.091</v>
@@ -2517,28 +2517,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M15">
-        <v>0.5487495000000001</v>
+        <v>0.5909610000000001</v>
       </c>
       <c r="N15">
-        <v>4.234583833333333</v>
+        <v>4.192372333333333</v>
       </c>
       <c r="O15">
-        <v>1.058645958333333</v>
+        <v>1.048093083333333</v>
       </c>
       <c r="P15">
-        <v>3.175937875</v>
+        <v>3.14427925</v>
       </c>
       <c r="Q15">
-        <v>6.605937875</v>
+        <v>6.57427925</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1429135779865224</v>
+        <v>0.1437889482586201</v>
       </c>
       <c r="T15">
-        <v>0.9391625213276574</v>
+        <v>0.9476280208889307</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.71678850428717</v>
+        <v>8.094160753980944</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1292759955024133</v>
+        <v>0.1290909281565521</v>
       </c>
       <c r="C16">
-        <v>76.2222194619972</v>
+        <v>75.62692190934014</v>
       </c>
       <c r="D16">
-        <v>87.17721946199721</v>
+        <v>87.37092190934015</v>
       </c>
       <c r="E16">
-        <v>-32.154</v>
+        <v>-31.365</v>
       </c>
       <c r="F16">
-        <v>11.046</v>
+        <v>11.835</v>
       </c>
       <c r="G16">
         <v>0.091</v>
@@ -2599,45 +2599,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M16">
-        <v>0.5909610000000001</v>
+        <v>0.6426405000000002</v>
       </c>
       <c r="N16">
-        <v>4.192372333333333</v>
+        <v>4.140692833333333</v>
       </c>
       <c r="O16">
-        <v>1.048093083333333</v>
+        <v>1.035173208333333</v>
       </c>
       <c r="P16">
-        <v>3.14427925</v>
+        <v>3.105519624999999</v>
       </c>
       <c r="Q16">
-        <v>6.57427925</v>
+        <v>6.535519624999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1437889482586201</v>
+        <v>0.1446849154782966</v>
       </c>
       <c r="T16">
-        <v>0.9476280208889307</v>
+        <v>0.9562927086751751</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.094160753980944</v>
+        <v>7.443249115692726</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1290909281565521</v>
+        <v>0.1288218608106909</v>
       </c>
       <c r="C17">
-        <v>75.62692190934015</v>
+        <v>75.12108422145931</v>
       </c>
       <c r="D17">
-        <v>87.37092190934015</v>
+        <v>87.65408422145931</v>
       </c>
       <c r="E17">
-        <v>-31.365</v>
+        <v>-30.576</v>
       </c>
       <c r="F17">
-        <v>11.835</v>
+        <v>12.624</v>
       </c>
       <c r="G17">
         <v>0.091</v>
@@ -2681,28 +2681,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M17">
-        <v>0.6426405000000001</v>
+        <v>0.6854832000000001</v>
       </c>
       <c r="N17">
-        <v>4.140692833333333</v>
+        <v>4.097850133333333</v>
       </c>
       <c r="O17">
-        <v>1.035173208333333</v>
+        <v>1.024462533333333</v>
       </c>
       <c r="P17">
-        <v>3.105519625</v>
+        <v>3.0733876</v>
       </c>
       <c r="Q17">
-        <v>6.535519625000001</v>
+        <v>6.5033876</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1446849154782966</v>
+        <v>0.1456022152508226</v>
       </c>
       <c r="T17">
-        <v>0.9562927086751751</v>
+        <v>0.9651636985515682</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.443249115692729</v>
+        <v>6.978046045961933</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1288218608106909</v>
+        <v>0.1285527934648298</v>
       </c>
       <c r="C18">
-        <v>75.12108422145931</v>
+        <v>74.61708791508548</v>
       </c>
       <c r="D18">
-        <v>87.65408422145931</v>
+        <v>87.93908791508548</v>
       </c>
       <c r="E18">
-        <v>-30.576</v>
+        <v>-29.787</v>
       </c>
       <c r="F18">
-        <v>12.624</v>
+        <v>13.413</v>
       </c>
       <c r="G18">
         <v>0.091</v>
@@ -2763,28 +2763,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M18">
-        <v>0.6854832000000001</v>
+        <v>0.7283259000000001</v>
       </c>
       <c r="N18">
-        <v>4.097850133333333</v>
+        <v>4.055007433333333</v>
       </c>
       <c r="O18">
-        <v>1.024462533333333</v>
+        <v>1.013751858333333</v>
       </c>
       <c r="P18">
-        <v>3.0733876</v>
+        <v>3.041255575</v>
       </c>
       <c r="Q18">
-        <v>6.5033876</v>
+        <v>6.471255575000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1456022152508226</v>
+        <v>0.146541618632325</v>
       </c>
       <c r="T18">
-        <v>0.9651636985515682</v>
+        <v>0.9742484472201637</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.978046045961933</v>
+        <v>6.567572749140643</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1285527934648298</v>
+        <v>0.1282837261189686</v>
       </c>
       <c r="C19">
-        <v>74.61708791508548</v>
+        <v>74.11495101034185</v>
       </c>
       <c r="D19">
-        <v>87.93908791508548</v>
+        <v>88.22595101034186</v>
       </c>
       <c r="E19">
-        <v>-29.787</v>
+        <v>-28.998</v>
       </c>
       <c r="F19">
-        <v>13.413</v>
+        <v>14.202</v>
       </c>
       <c r="G19">
         <v>0.091</v>
@@ -2845,28 +2845,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M19">
-        <v>0.7283259000000001</v>
+        <v>0.7711686000000002</v>
       </c>
       <c r="N19">
-        <v>4.055007433333333</v>
+        <v>4.012164733333333</v>
       </c>
       <c r="O19">
-        <v>1.013751858333333</v>
+        <v>1.003041183333333</v>
       </c>
       <c r="P19">
-        <v>3.041255575</v>
+        <v>3.00912355</v>
       </c>
       <c r="Q19">
-        <v>6.471255575000001</v>
+        <v>6.43912355</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.146541618632325</v>
+        <v>0.1475039342914251</v>
       </c>
       <c r="T19">
-        <v>0.9742484472201637</v>
+        <v>0.9835547751245782</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.567572749140643</v>
+        <v>6.202707596410606</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1282837261189686</v>
+        <v>0.1281571587731074</v>
       </c>
       <c r="C20">
-        <v>74.11495101034183</v>
+        <v>73.46153757770045</v>
       </c>
       <c r="D20">
-        <v>88.22595101034183</v>
+        <v>88.36153757770046</v>
       </c>
       <c r="E20">
-        <v>-28.998</v>
+        <v>-28.209</v>
       </c>
       <c r="F20">
-        <v>14.202</v>
+        <v>14.991</v>
       </c>
       <c r="G20">
         <v>0.091</v>
@@ -2927,45 +2927,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M20">
-        <v>0.7711686</v>
+        <v>0.8290023000000001</v>
       </c>
       <c r="N20">
-        <v>4.012164733333333</v>
+        <v>3.954331033333333</v>
       </c>
       <c r="O20">
-        <v>1.003041183333333</v>
+        <v>0.9885827583333333</v>
       </c>
       <c r="P20">
-        <v>3.00912355</v>
+        <v>2.965748275</v>
       </c>
       <c r="Q20">
-        <v>6.43912355</v>
+        <v>6.395748275000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1475039342914251</v>
+        <v>0.1484900108309968</v>
       </c>
       <c r="T20">
-        <v>0.9835547751245782</v>
+        <v>0.9930908889031762</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.202707596410607</v>
+        <v>5.769988012498075</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1281571587731074</v>
+        <v>0.1278955914272463</v>
       </c>
       <c r="C21">
-        <v>73.46153757770045</v>
+        <v>72.95406905166388</v>
       </c>
       <c r="D21">
-        <v>88.36153757770046</v>
+        <v>88.64306905166389</v>
       </c>
       <c r="E21">
-        <v>-28.209</v>
+        <v>-27.42</v>
       </c>
       <c r="F21">
-        <v>14.991</v>
+        <v>15.78</v>
       </c>
       <c r="G21">
         <v>0.091</v>
@@ -3009,28 +3009,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M21">
-        <v>0.8290023000000001</v>
+        <v>0.8726340000000001</v>
       </c>
       <c r="N21">
-        <v>3.954331033333333</v>
+        <v>3.910699333333333</v>
       </c>
       <c r="O21">
-        <v>0.9885827583333333</v>
+        <v>0.9776748333333333</v>
       </c>
       <c r="P21">
-        <v>2.965748275</v>
+        <v>2.9330245</v>
       </c>
       <c r="Q21">
-        <v>6.395748275000001</v>
+        <v>6.3630245</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1484900108309968</v>
+        <v>0.1495007392840578</v>
       </c>
       <c r="T21">
-        <v>0.9930908889031762</v>
+        <v>1.002865405526239</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.769988012498075</v>
+        <v>5.48148861187317</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1278955914272463</v>
+        <v>0.1276340240813851</v>
       </c>
       <c r="C22">
-        <v>72.95406905166388</v>
+        <v>72.44840025236073</v>
       </c>
       <c r="D22">
-        <v>88.64306905166389</v>
+        <v>88.92640025236074</v>
       </c>
       <c r="E22">
-        <v>-27.42</v>
+        <v>-26.631</v>
       </c>
       <c r="F22">
-        <v>15.78</v>
+        <v>16.569</v>
       </c>
       <c r="G22">
         <v>0.091</v>
@@ -3091,28 +3091,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M22">
-        <v>0.8726340000000001</v>
+        <v>0.9162657000000002</v>
       </c>
       <c r="N22">
-        <v>3.910699333333333</v>
+        <v>3.867067633333333</v>
       </c>
       <c r="O22">
-        <v>0.9776748333333333</v>
+        <v>0.9667669083333332</v>
       </c>
       <c r="P22">
-        <v>2.9330245</v>
+        <v>2.900300725</v>
       </c>
       <c r="Q22">
-        <v>6.3630245</v>
+        <v>6.330300725</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1495007392840578</v>
+        <v>0.1505370557992216</v>
       </c>
       <c r="T22">
-        <v>1.002865405526239</v>
+        <v>1.012887378266341</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.48148861187317</v>
+        <v>5.220465344641115</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1276340240813851</v>
+        <v>0.1273724567355239</v>
       </c>
       <c r="C23">
-        <v>72.44840025236073</v>
+        <v>71.94454849261065</v>
       </c>
       <c r="D23">
-        <v>88.92640025236074</v>
+        <v>89.21154849261066</v>
       </c>
       <c r="E23">
-        <v>-26.631</v>
+        <v>-25.842</v>
       </c>
       <c r="F23">
-        <v>16.569</v>
+        <v>17.358</v>
       </c>
       <c r="G23">
         <v>0.091</v>
@@ -3173,28 +3173,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M23">
-        <v>0.9162657</v>
+        <v>0.9598974</v>
       </c>
       <c r="N23">
-        <v>3.867067633333333</v>
+        <v>3.823435933333333</v>
       </c>
       <c r="O23">
-        <v>0.9667669083333333</v>
+        <v>0.9558589833333333</v>
       </c>
       <c r="P23">
-        <v>2.900300725</v>
+        <v>2.86757695</v>
       </c>
       <c r="Q23">
-        <v>6.330300725000001</v>
+        <v>6.29757695</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1505370557992216</v>
+        <v>0.151599944532723</v>
       </c>
       <c r="T23">
-        <v>1.012887378266341</v>
+        <v>1.023166324666446</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.220465344641116</v>
+        <v>4.983171465339247</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1273724567355239</v>
+        <v>0.1271108893896628</v>
       </c>
       <c r="C24">
-        <v>71.94454849261065</v>
+        <v>71.44253130800638</v>
       </c>
       <c r="D24">
-        <v>89.21154849261066</v>
+        <v>89.49853130800639</v>
       </c>
       <c r="E24">
-        <v>-25.842</v>
+        <v>-25.053</v>
       </c>
       <c r="F24">
-        <v>17.358</v>
+        <v>18.147</v>
       </c>
       <c r="G24">
         <v>0.091</v>
@@ -3255,28 +3255,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M24">
-        <v>0.9598974</v>
+        <v>1.0035291</v>
       </c>
       <c r="N24">
-        <v>3.823435933333333</v>
+        <v>3.779804233333333</v>
       </c>
       <c r="O24">
-        <v>0.9558589833333333</v>
+        <v>0.9449510583333333</v>
       </c>
       <c r="P24">
-        <v>2.86757695</v>
+        <v>2.834853175</v>
       </c>
       <c r="Q24">
-        <v>6.29757695</v>
+        <v>6.264853175</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.151599944532723</v>
+        <v>0.1526904407657958</v>
       </c>
       <c r="T24">
-        <v>1.023166324666446</v>
+        <v>1.033712256687333</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.983171465339247</v>
+        <v>4.766511836411453</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1271108893896628</v>
+        <v>0.1268493220438016</v>
       </c>
       <c r="C25">
-        <v>71.44253130800638</v>
+        <v>70.94236646050842</v>
       </c>
       <c r="D25">
-        <v>89.49853130800639</v>
+        <v>89.78736646050844</v>
       </c>
       <c r="E25">
-        <v>-25.053</v>
+        <v>-24.264</v>
       </c>
       <c r="F25">
-        <v>18.147</v>
+        <v>18.936</v>
       </c>
       <c r="G25">
         <v>0.091</v>
@@ -3337,28 +3337,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M25">
-        <v>1.0035291</v>
+        <v>1.0471608</v>
       </c>
       <c r="N25">
-        <v>3.779804233333333</v>
+        <v>3.736172533333333</v>
       </c>
       <c r="O25">
-        <v>0.9449510583333333</v>
+        <v>0.9340431333333332</v>
       </c>
       <c r="P25">
-        <v>2.834853175</v>
+        <v>2.8021294</v>
       </c>
       <c r="Q25">
-        <v>6.264853175</v>
+        <v>6.2321294</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1526904407657958</v>
+        <v>0.1538096342681599</v>
       </c>
       <c r="T25">
-        <v>1.033712256687333</v>
+        <v>1.044535713235085</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.766511836411453</v>
+        <v>4.567907176560975</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1268493220438016</v>
+        <v>0.1270565046979404</v>
       </c>
       <c r="C26">
-        <v>70.94236646050842</v>
+        <v>69.92443235904085</v>
       </c>
       <c r="D26">
-        <v>89.78736646050844</v>
+        <v>89.55843235904085</v>
       </c>
       <c r="E26">
-        <v>-24.264</v>
+        <v>-23.475</v>
       </c>
       <c r="F26">
-        <v>18.936</v>
+        <v>19.725</v>
       </c>
       <c r="G26">
         <v>0.091</v>
@@ -3419,45 +3419,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M26">
-        <v>1.0471608</v>
+        <v>1.140105</v>
       </c>
       <c r="N26">
-        <v>3.736172533333333</v>
+        <v>3.643228333333333</v>
       </c>
       <c r="O26">
-        <v>0.9340431333333332</v>
+        <v>0.9108070833333333</v>
       </c>
       <c r="P26">
-        <v>2.8021294</v>
+        <v>2.73242125</v>
       </c>
       <c r="Q26">
-        <v>6.2321294</v>
+        <v>6.16242125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1538096342681599</v>
+        <v>0.1549586729305872</v>
       </c>
       <c r="T26">
-        <v>1.044535713235085</v>
+        <v>1.055647795290778</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.567907176560976</v>
+        <v>4.195520003274551</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1270565046979404</v>
+        <v>0.1268136873520792</v>
       </c>
       <c r="C27">
-        <v>69.92443235904085</v>
+        <v>69.40386034393677</v>
       </c>
       <c r="D27">
-        <v>89.55843235904085</v>
+        <v>89.82686034393679</v>
       </c>
       <c r="E27">
-        <v>-23.475</v>
+        <v>-22.686</v>
       </c>
       <c r="F27">
-        <v>19.725</v>
+        <v>20.514</v>
       </c>
       <c r="G27">
         <v>0.091</v>
@@ -3501,28 +3501,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M27">
-        <v>1.140105</v>
+        <v>1.1857092</v>
       </c>
       <c r="N27">
-        <v>3.643228333333333</v>
+        <v>3.597624133333333</v>
       </c>
       <c r="O27">
-        <v>0.9108070833333333</v>
+        <v>0.8994060333333332</v>
       </c>
       <c r="P27">
-        <v>2.73242125</v>
+        <v>2.6982181</v>
       </c>
       <c r="Q27">
-        <v>6.16242125</v>
+        <v>6.1282181</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1549586729305872</v>
+        <v>0.1561387666919989</v>
       </c>
       <c r="T27">
-        <v>1.055647795290778</v>
+        <v>1.067060203888516</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.195520003274551</v>
+        <v>4.034153849302453</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1268136873520792</v>
+        <v>0.1272796200062181</v>
       </c>
       <c r="C28">
-        <v>69.40386034393677</v>
+        <v>68.10119487213146</v>
       </c>
       <c r="D28">
-        <v>89.82686034393679</v>
+        <v>89.31319487213148</v>
       </c>
       <c r="E28">
-        <v>-22.686</v>
+        <v>-21.897</v>
       </c>
       <c r="F28">
-        <v>20.514</v>
+        <v>21.303</v>
       </c>
       <c r="G28">
         <v>0.091</v>
@@ -3583,45 +3583,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M28">
-        <v>1.1857092</v>
+        <v>1.3058739</v>
       </c>
       <c r="N28">
-        <v>3.597624133333333</v>
+        <v>3.477459433333333</v>
       </c>
       <c r="O28">
-        <v>0.8994060333333332</v>
+        <v>0.8693648583333332</v>
       </c>
       <c r="P28">
-        <v>2.6982181</v>
+        <v>2.608094575</v>
       </c>
       <c r="Q28">
-        <v>6.1282181</v>
+        <v>6.038094575</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1561387666919989</v>
+        <v>0.1573511917893398</v>
       </c>
       <c r="T28">
-        <v>1.067060203888516</v>
+        <v>1.078785281214959</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.034153849302453</v>
+        <v>3.662936623002674</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1272796200062181</v>
+        <v>0.1270630526603569</v>
       </c>
       <c r="C29">
-        <v>68.10119487213146</v>
+        <v>67.5502159768109</v>
       </c>
       <c r="D29">
-        <v>89.31319487213148</v>
+        <v>89.55121597681091</v>
       </c>
       <c r="E29">
-        <v>-21.897</v>
+        <v>-21.108</v>
       </c>
       <c r="F29">
-        <v>21.303</v>
+        <v>22.092</v>
       </c>
       <c r="G29">
         <v>0.091</v>
@@ -3665,28 +3665,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M29">
-        <v>1.3058739</v>
+        <v>1.3542396</v>
       </c>
       <c r="N29">
-        <v>3.477459433333333</v>
+        <v>3.429093733333333</v>
       </c>
       <c r="O29">
-        <v>0.8693648583333332</v>
+        <v>0.8572734333333333</v>
       </c>
       <c r="P29">
-        <v>2.608094575</v>
+        <v>2.5718203</v>
       </c>
       <c r="Q29">
-        <v>6.038094575</v>
+        <v>6.0018203</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1573511917893398</v>
+        <v>0.1585972953616068</v>
       </c>
       <c r="T29">
-        <v>1.078785281214959</v>
+        <v>1.090836055133804</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.662936623002674</v>
+        <v>3.532117457895437</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1270630526603569</v>
+        <v>0.1274554853144957</v>
       </c>
       <c r="C30">
-        <v>67.5502159768109</v>
+        <v>66.33083679001426</v>
       </c>
       <c r="D30">
-        <v>89.55121597681091</v>
+        <v>89.12083679001427</v>
       </c>
       <c r="E30">
-        <v>-21.108</v>
+        <v>-20.319</v>
       </c>
       <c r="F30">
-        <v>22.092</v>
+        <v>22.881</v>
       </c>
       <c r="G30">
         <v>0.091</v>
@@ -3747,45 +3747,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M30">
-        <v>1.3542396</v>
+        <v>1.4666721</v>
       </c>
       <c r="N30">
-        <v>3.429093733333333</v>
+        <v>3.316661233333333</v>
       </c>
       <c r="O30">
-        <v>0.8572734333333333</v>
+        <v>0.8291653083333332</v>
       </c>
       <c r="P30">
-        <v>2.5718203</v>
+        <v>2.487495925</v>
       </c>
       <c r="Q30">
-        <v>6.0018203</v>
+        <v>5.917495925</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1585972953616068</v>
+        <v>0.1598785004429517</v>
       </c>
       <c r="T30">
-        <v>1.090836055133804</v>
+        <v>1.103226287472897</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.532117457895437</v>
+        <v>3.261351554538559</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1274554853144957</v>
+        <v>0.1272599179686345</v>
       </c>
       <c r="C31">
-        <v>66.33083679001427</v>
+        <v>65.75579631693964</v>
       </c>
       <c r="D31">
-        <v>89.12083679001428</v>
+        <v>89.33479631693965</v>
       </c>
       <c r="E31">
-        <v>-20.319</v>
+        <v>-19.53</v>
       </c>
       <c r="F31">
-        <v>22.881</v>
+        <v>23.67</v>
       </c>
       <c r="G31">
         <v>0.091</v>
@@ -3829,28 +3829,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M31">
-        <v>1.4666721</v>
+        <v>1.517247</v>
       </c>
       <c r="N31">
-        <v>3.316661233333333</v>
+        <v>3.266086333333333</v>
       </c>
       <c r="O31">
-        <v>0.8291653083333332</v>
+        <v>0.8165215833333332</v>
       </c>
       <c r="P31">
-        <v>2.487495925</v>
+        <v>2.44956475</v>
       </c>
       <c r="Q31">
-        <v>5.917495925</v>
+        <v>5.87956475</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1598785004429517</v>
+        <v>0.1611963113837636</v>
       </c>
       <c r="T31">
-        <v>1.103226287472897</v>
+        <v>1.115970526450251</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.261351554538559</v>
+        <v>3.15263983605394</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1272599179686345</v>
+        <v>0.1270643506227733</v>
       </c>
       <c r="C32">
-        <v>65.75579631693964</v>
+        <v>65.18178565574398</v>
       </c>
       <c r="D32">
-        <v>89.33479631693965</v>
+        <v>89.54978565574399</v>
       </c>
       <c r="E32">
-        <v>-19.53</v>
+        <v>-18.741</v>
       </c>
       <c r="F32">
-        <v>23.67</v>
+        <v>24.459</v>
       </c>
       <c r="G32">
         <v>0.091</v>
@@ -3911,28 +3911,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M32">
-        <v>1.517247</v>
+        <v>1.5678219</v>
       </c>
       <c r="N32">
-        <v>3.266086333333333</v>
+        <v>3.215511433333333</v>
       </c>
       <c r="O32">
-        <v>0.8165215833333332</v>
+        <v>0.8038778583333333</v>
       </c>
       <c r="P32">
-        <v>2.44956475</v>
+        <v>2.411633575</v>
       </c>
       <c r="Q32">
-        <v>5.87956475</v>
+        <v>5.841633574999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1611963113837636</v>
+        <v>0.1625523197431498</v>
       </c>
       <c r="T32">
-        <v>1.115970526450251</v>
+        <v>1.129084163658832</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.15263983605394</v>
+        <v>3.050941776826394</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1270643506227733</v>
+        <v>0.1287407832769122</v>
       </c>
       <c r="C33">
-        <v>65.18178565574398</v>
+        <v>62.5827691727406</v>
       </c>
       <c r="D33">
-        <v>89.54978565574399</v>
+        <v>87.73976917274061</v>
       </c>
       <c r="E33">
-        <v>-18.741</v>
+        <v>-17.952</v>
       </c>
       <c r="F33">
-        <v>24.459</v>
+        <v>25.248</v>
       </c>
       <c r="G33">
         <v>0.091</v>
@@ -3993,45 +3993,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M33">
-        <v>1.5678219</v>
+        <v>1.8153312</v>
       </c>
       <c r="N33">
-        <v>3.215511433333333</v>
+        <v>2.968002133333333</v>
       </c>
       <c r="O33">
-        <v>0.8038778583333333</v>
+        <v>0.7420005333333333</v>
       </c>
       <c r="P33">
-        <v>2.411633575</v>
+        <v>2.2260016</v>
       </c>
       <c r="Q33">
-        <v>5.841633574999999</v>
+        <v>5.6560016</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1625523197431498</v>
+        <v>0.1639482107013414</v>
       </c>
       <c r="T33">
-        <v>1.129084163658832</v>
+        <v>1.14258349607943</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.050941776826394</v>
+        <v>2.634964536131662</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1287407832769122</v>
+        <v>0.128603715931051</v>
       </c>
       <c r="C34">
-        <v>62.5827691727406</v>
+        <v>61.93900730791067</v>
       </c>
       <c r="D34">
-        <v>87.73976917274061</v>
+        <v>87.88500730791068</v>
       </c>
       <c r="E34">
-        <v>-17.952</v>
+        <v>-17.163</v>
       </c>
       <c r="F34">
-        <v>25.248</v>
+        <v>26.037</v>
       </c>
       <c r="G34">
         <v>0.091</v>
@@ -4075,28 +4075,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M34">
-        <v>1.8153312</v>
+        <v>1.8720603</v>
       </c>
       <c r="N34">
-        <v>2.968002133333333</v>
+        <v>2.911273033333333</v>
       </c>
       <c r="O34">
-        <v>0.7420005333333333</v>
+        <v>0.7278182583333332</v>
       </c>
       <c r="P34">
-        <v>2.2260016</v>
+        <v>2.183454775</v>
       </c>
       <c r="Q34">
-        <v>5.6560016</v>
+        <v>5.613454774999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1639482107013414</v>
+        <v>0.1653857700463448</v>
       </c>
       <c r="T34">
-        <v>1.14258349607943</v>
+        <v>1.156485793646912</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.634964536131662</v>
+        <v>2.555117125945854</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.128603715931051</v>
+        <v>0.1294611485851898</v>
       </c>
       <c r="C35">
-        <v>61.93900730791067</v>
+        <v>60.24928485370842</v>
       </c>
       <c r="D35">
-        <v>87.88500730791068</v>
+        <v>86.98428485370843</v>
       </c>
       <c r="E35">
-        <v>-17.163</v>
+        <v>-16.374</v>
       </c>
       <c r="F35">
-        <v>26.037</v>
+        <v>26.826</v>
       </c>
       <c r="G35">
         <v>0.091</v>
@@ -4157,45 +4157,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M35">
-        <v>1.8720603</v>
+        <v>2.0334108</v>
       </c>
       <c r="N35">
-        <v>2.911273033333333</v>
+        <v>2.749922533333333</v>
       </c>
       <c r="O35">
-        <v>0.7278182583333332</v>
+        <v>0.6874806333333332</v>
       </c>
       <c r="P35">
-        <v>2.183454775</v>
+        <v>2.0624419</v>
       </c>
       <c r="Q35">
-        <v>5.613454774999999</v>
+        <v>5.492441899999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1653857700463448</v>
+        <v>0.1668668917957422</v>
       </c>
       <c r="T35">
-        <v>1.156485793646912</v>
+        <v>1.170809372958863</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.555117125945854</v>
+        <v>2.352369394975837</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1294611485851898</v>
+        <v>0.1293533312393286</v>
       </c>
       <c r="C36">
-        <v>60.24928485370842</v>
+        <v>59.57252950733803</v>
       </c>
       <c r="D36">
-        <v>86.98428485370843</v>
+        <v>87.09652950733805</v>
       </c>
       <c r="E36">
-        <v>-16.374</v>
+        <v>-15.585</v>
       </c>
       <c r="F36">
-        <v>26.826</v>
+        <v>27.61500000000001</v>
       </c>
       <c r="G36">
         <v>0.091</v>
@@ -4239,28 +4239,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M36">
-        <v>2.0334108</v>
+        <v>2.093217000000001</v>
       </c>
       <c r="N36">
-        <v>2.749922533333333</v>
+        <v>2.690116333333333</v>
       </c>
       <c r="O36">
-        <v>0.6874806333333332</v>
+        <v>0.6725290833333332</v>
       </c>
       <c r="P36">
-        <v>2.0624419</v>
+        <v>2.01758725</v>
       </c>
       <c r="Q36">
-        <v>5.492441899999999</v>
+        <v>5.44758725</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1668668917957422</v>
+        <v>0.1683935865220441</v>
       </c>
       <c r="T36">
-        <v>1.170809372958863</v>
+        <v>1.185573677788104</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.352369394975837</v>
+        <v>2.28515884083367</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1293533312393286</v>
+        <v>0.1292455138934674</v>
       </c>
       <c r="C37">
-        <v>59.57252950733803</v>
+        <v>58.89606421659981</v>
       </c>
       <c r="D37">
-        <v>87.09652950733805</v>
+        <v>87.20906421659983</v>
       </c>
       <c r="E37">
-        <v>-15.585</v>
+        <v>-14.796</v>
       </c>
       <c r="F37">
-        <v>27.61500000000001</v>
+        <v>28.40400000000001</v>
       </c>
       <c r="G37">
         <v>0.091</v>
@@ -4321,28 +4321,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M37">
-        <v>2.093217000000001</v>
+        <v>2.153023200000001</v>
       </c>
       <c r="N37">
-        <v>2.690116333333333</v>
+        <v>2.630310133333333</v>
       </c>
       <c r="O37">
-        <v>0.6725290833333332</v>
+        <v>0.6575775333333331</v>
       </c>
       <c r="P37">
-        <v>2.01758725</v>
+        <v>1.972732599999999</v>
       </c>
       <c r="Q37">
-        <v>5.44758725</v>
+        <v>5.402732599999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1683935865220441</v>
+        <v>0.1699679904585429</v>
       </c>
       <c r="T37">
-        <v>1.185573677788104</v>
+        <v>1.20079936714326</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.28515884083367</v>
+        <v>2.221682206366068</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1292455138934675</v>
+        <v>0.1291376965476063</v>
       </c>
       <c r="C38">
-        <v>58.89606421659981</v>
+        <v>58.21989010726378</v>
       </c>
       <c r="D38">
-        <v>87.20906421659981</v>
+        <v>87.32189010726378</v>
       </c>
       <c r="E38">
-        <v>-14.796</v>
+        <v>-14.007</v>
       </c>
       <c r="F38">
-        <v>28.404</v>
+        <v>29.193</v>
       </c>
       <c r="G38">
         <v>0.091</v>
@@ -4403,28 +4403,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M38">
-        <v>2.1530232</v>
+        <v>2.2128294</v>
       </c>
       <c r="N38">
-        <v>2.630310133333333</v>
+        <v>2.570503933333333</v>
       </c>
       <c r="O38">
-        <v>0.6575775333333332</v>
+        <v>0.6426259833333332</v>
       </c>
       <c r="P38">
-        <v>1.9727326</v>
+        <v>1.92787795</v>
       </c>
       <c r="Q38">
-        <v>5.4027326</v>
+        <v>5.35787795</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1699679904585429</v>
+        <v>0.171592375472391</v>
       </c>
       <c r="T38">
-        <v>1.20079936714326</v>
+        <v>1.216508411716039</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.221682206366068</v>
+        <v>2.161636741329147</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1291376965476063</v>
+        <v>0.1290298792017451</v>
       </c>
       <c r="C39">
-        <v>58.21989010726378</v>
+        <v>57.54400831093352</v>
       </c>
       <c r="D39">
-        <v>87.32189010726378</v>
+        <v>87.43500831093353</v>
       </c>
       <c r="E39">
-        <v>-14.007</v>
+        <v>-13.218</v>
       </c>
       <c r="F39">
-        <v>29.193</v>
+        <v>29.982</v>
       </c>
       <c r="G39">
         <v>0.091</v>
@@ -4485,28 +4485,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M39">
-        <v>2.2128294</v>
+        <v>2.272635600000001</v>
       </c>
       <c r="N39">
-        <v>2.570503933333333</v>
+        <v>2.510697733333333</v>
       </c>
       <c r="O39">
-        <v>0.6426259833333332</v>
+        <v>0.6276744333333332</v>
       </c>
       <c r="P39">
-        <v>1.92787795</v>
+        <v>1.8830233</v>
       </c>
       <c r="Q39">
-        <v>5.35787795</v>
+        <v>5.313023299999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.171592375472391</v>
+        <v>0.1732691600028147</v>
       </c>
       <c r="T39">
-        <v>1.216508411716039</v>
+        <v>1.232724199662134</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.161636741329147</v>
+        <v>2.104751563925749</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1290298792017451</v>
+        <v>0.128922061855884</v>
       </c>
       <c r="C40">
-        <v>57.54400831093352</v>
+        <v>56.86841996508349</v>
       </c>
       <c r="D40">
-        <v>87.43500831093353</v>
+        <v>87.5484199650835</v>
       </c>
       <c r="E40">
-        <v>-13.218</v>
+        <v>-12.429</v>
       </c>
       <c r="F40">
-        <v>29.982</v>
+        <v>30.771</v>
       </c>
       <c r="G40">
         <v>0.091</v>
@@ -4567,28 +4567,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M40">
-        <v>2.272635600000001</v>
+        <v>2.332441800000001</v>
       </c>
       <c r="N40">
-        <v>2.510697733333333</v>
+        <v>2.450891533333333</v>
       </c>
       <c r="O40">
-        <v>0.6276744333333332</v>
+        <v>0.6127228833333331</v>
       </c>
       <c r="P40">
-        <v>1.8830233</v>
+        <v>1.838168649999999</v>
       </c>
       <c r="Q40">
-        <v>5.313023299999999</v>
+        <v>5.26816865</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1732691600028147</v>
+        <v>0.1750009210752196</v>
       </c>
       <c r="T40">
-        <v>1.232724199662134</v>
+        <v>1.24947165278679</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.104751563925749</v>
+        <v>2.05078357510714</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.128922061855884</v>
+        <v>0.1330742445100228</v>
       </c>
       <c r="C41">
-        <v>56.86841996508349</v>
+        <v>51.9141930666194</v>
       </c>
       <c r="D41">
-        <v>87.5484199650835</v>
+        <v>83.38319306661941</v>
       </c>
       <c r="E41">
-        <v>-12.429</v>
+        <v>-11.64</v>
       </c>
       <c r="F41">
-        <v>30.771</v>
+        <v>31.56</v>
       </c>
       <c r="G41">
         <v>0.091</v>
@@ -4649,45 +4649,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M41">
-        <v>2.332441800000001</v>
+        <v>2.8404</v>
       </c>
       <c r="N41">
-        <v>2.450891533333333</v>
+        <v>1.942933333333333</v>
       </c>
       <c r="O41">
-        <v>0.6127228833333331</v>
+        <v>0.4857333333333332</v>
       </c>
       <c r="P41">
-        <v>1.838168649999999</v>
+        <v>1.4572</v>
       </c>
       <c r="Q41">
-        <v>5.26816865</v>
+        <v>4.8872</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1750009210752196</v>
+        <v>0.1767904075167046</v>
       </c>
       <c r="T41">
-        <v>1.24947165278679</v>
+        <v>1.266777354348933</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.05078357510714</v>
+        <v>1.68403511242548</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1330742445100228</v>
+        <v>0.1330729271641616</v>
       </c>
       <c r="C42">
-        <v>51.9141930666194</v>
+        <v>51.12645169868145</v>
       </c>
       <c r="D42">
-        <v>83.38319306661941</v>
+        <v>83.38445169868146</v>
       </c>
       <c r="E42">
-        <v>-11.64</v>
+        <v>-10.851</v>
       </c>
       <c r="F42">
-        <v>31.56</v>
+        <v>32.349</v>
       </c>
       <c r="G42">
         <v>0.091</v>
@@ -4731,28 +4731,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M42">
-        <v>2.8404</v>
+        <v>2.91141</v>
       </c>
       <c r="N42">
-        <v>1.942933333333333</v>
+        <v>1.871923333333333</v>
       </c>
       <c r="O42">
-        <v>0.4857333333333332</v>
+        <v>0.4679808333333333</v>
       </c>
       <c r="P42">
-        <v>1.4572</v>
+        <v>1.4039425</v>
       </c>
       <c r="Q42">
-        <v>4.8872</v>
+        <v>4.8339425</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1767904075167046</v>
+        <v>0.1786405545155281</v>
       </c>
       <c r="T42">
-        <v>1.266777354348933</v>
+        <v>1.284669689862336</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.68403511242548</v>
+        <v>1.642961085293151</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1330729271641616</v>
+        <v>0.1330716098183004</v>
       </c>
       <c r="C43">
-        <v>51.12645169868145</v>
+        <v>50.33871036874105</v>
       </c>
       <c r="D43">
-        <v>83.38445169868146</v>
+        <v>83.38571036874106</v>
       </c>
       <c r="E43">
-        <v>-10.851</v>
+        <v>-10.062</v>
       </c>
       <c r="F43">
-        <v>32.349</v>
+        <v>33.13800000000001</v>
       </c>
       <c r="G43">
         <v>0.091</v>
@@ -4813,28 +4813,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M43">
-        <v>2.91141</v>
+        <v>2.98242</v>
       </c>
       <c r="N43">
-        <v>1.871923333333333</v>
+        <v>1.800913333333333</v>
       </c>
       <c r="O43">
-        <v>0.4679808333333333</v>
+        <v>0.4502283333333332</v>
       </c>
       <c r="P43">
-        <v>1.4039425</v>
+        <v>1.350685</v>
       </c>
       <c r="Q43">
-        <v>4.8339425</v>
+        <v>4.780685</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1786405545155281</v>
+        <v>0.1805544996867249</v>
       </c>
       <c r="T43">
-        <v>1.284669689862336</v>
+        <v>1.303179002462408</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.642961085293151</v>
+        <v>1.603842964214742</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1330716098183004</v>
+        <v>0.1330702924724393</v>
       </c>
       <c r="C44">
-        <v>50.33871036874105</v>
+        <v>49.55096907679989</v>
       </c>
       <c r="D44">
-        <v>83.38571036874106</v>
+        <v>83.3869690767999</v>
       </c>
       <c r="E44">
-        <v>-10.062</v>
+        <v>-9.273000000000003</v>
       </c>
       <c r="F44">
-        <v>33.138</v>
+        <v>33.927</v>
       </c>
       <c r="G44">
         <v>0.091</v>
@@ -4895,28 +4895,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M44">
-        <v>2.98242</v>
+        <v>3.05343</v>
       </c>
       <c r="N44">
-        <v>1.800913333333333</v>
+        <v>1.729903333333334</v>
       </c>
       <c r="O44">
-        <v>0.4502283333333333</v>
+        <v>0.4324758333333334</v>
       </c>
       <c r="P44">
-        <v>1.350685</v>
+        <v>1.2974275</v>
       </c>
       <c r="Q44">
-        <v>4.780685</v>
+        <v>4.7274275</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1805544996867249</v>
+        <v>0.1825356008288408</v>
       </c>
       <c r="T44">
-        <v>1.303179002462408</v>
+        <v>1.322337764627395</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.603842964214743</v>
+        <v>1.566544290628354</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1330702924724393</v>
+        <v>0.1330689751265781</v>
       </c>
       <c r="C45">
-        <v>49.55096907679989</v>
+        <v>48.76322782285977</v>
       </c>
       <c r="D45">
-        <v>83.3869690767999</v>
+        <v>83.38822782285978</v>
       </c>
       <c r="E45">
-        <v>-9.273000000000003</v>
+        <v>-8.484000000000002</v>
       </c>
       <c r="F45">
-        <v>33.927</v>
+        <v>34.716</v>
       </c>
       <c r="G45">
         <v>0.091</v>
@@ -4977,28 +4977,28 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M45">
-        <v>3.05343</v>
+        <v>3.12444</v>
       </c>
       <c r="N45">
-        <v>1.729903333333334</v>
+        <v>1.658893333333333</v>
       </c>
       <c r="O45">
-        <v>0.4324758333333334</v>
+        <v>0.4147233333333333</v>
       </c>
       <c r="P45">
-        <v>1.2974275</v>
+        <v>1.24417</v>
       </c>
       <c r="Q45">
-        <v>4.7274275</v>
+        <v>4.67417</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1825356008288408</v>
+        <v>0.1845874555831751</v>
       </c>
       <c r="T45">
-        <v>1.322337764627395</v>
+        <v>1.342180768298275</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.566544290628354</v>
+        <v>1.530941011295891</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1330689751265781</v>
+        <v>0.1544045823197364</v>
       </c>
       <c r="C46">
-        <v>48.76322782285977</v>
+        <v>31.59242849763175</v>
       </c>
       <c r="D46">
-        <v>83.38822782285978</v>
+        <v>67.00642849763176</v>
       </c>
       <c r="E46">
-        <v>-8.484000000000002</v>
+        <v>-7.695</v>
       </c>
       <c r="F46">
-        <v>34.716</v>
+        <v>35.505</v>
       </c>
       <c r="G46">
         <v>0.091</v>
@@ -5059,45 +5059,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M46">
-        <v>3.12444</v>
+        <v>5.212134000000001</v>
       </c>
       <c r="N46">
-        <v>1.658893333333333</v>
+        <v>-0.4288006666666675</v>
       </c>
       <c r="O46">
-        <v>0.4147233333333333</v>
+        <v>-0.1072001666666669</v>
       </c>
       <c r="P46">
-        <v>1.24417</v>
+        <v>-0.3216005000000006</v>
       </c>
       <c r="Q46">
-        <v>4.67417</v>
+        <v>3.1083995</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1845874555831751</v>
+        <v>0.1881834515119376</v>
       </c>
       <c r="T46">
-        <v>1.342180768298275</v>
+        <v>1.376956797285789</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.25</v>
+        <v>0.2294325766247247</v>
       </c>
       <c r="W46">
-        <v>0.0675</v>
+        <v>0.1131192977514904</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.530941011295891</v>
+        <v>0.9177303064988991</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1544045823197364</v>
+        <v>0.1554145823197364</v>
       </c>
       <c r="C47">
-        <v>31.59242849763175</v>
+        <v>30.18602439545487</v>
       </c>
       <c r="D47">
-        <v>67.00642849763176</v>
+        <v>66.38902439545488</v>
       </c>
       <c r="E47">
-        <v>-7.695</v>
+        <v>-6.905999999999999</v>
       </c>
       <c r="F47">
-        <v>35.505</v>
+        <v>36.294</v>
       </c>
       <c r="G47">
         <v>0.091</v>
@@ -5141,37 +5141,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M47">
-        <v>5.212134000000001</v>
+        <v>5.327959200000001</v>
       </c>
       <c r="N47">
-        <v>-0.4288006666666675</v>
+        <v>-0.5446258666666681</v>
       </c>
       <c r="O47">
-        <v>-0.1072001666666669</v>
+        <v>-0.136156466666667</v>
       </c>
       <c r="P47">
-        <v>-0.3216005000000006</v>
+        <v>-0.4084694000000011</v>
       </c>
       <c r="Q47">
-        <v>3.1083995</v>
+        <v>3.021530599999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1881834515119376</v>
+        <v>0.190820182095492</v>
       </c>
       <c r="T47">
-        <v>1.376956797285789</v>
+        <v>1.402455997235526</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2294325766247247</v>
+        <v>0.2244449119154916</v>
       </c>
       <c r="W47">
-        <v>0.1131192977514904</v>
+        <v>0.1138514869308058</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9177303064988991</v>
+        <v>0.8977796476619664</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1554145823197364</v>
+        <v>0.1564245823197364</v>
       </c>
       <c r="C48">
-        <v>30.18602439545487</v>
+        <v>28.7908940649863</v>
       </c>
       <c r="D48">
-        <v>66.38902439545488</v>
+        <v>65.78289406498631</v>
       </c>
       <c r="E48">
-        <v>-6.905999999999999</v>
+        <v>-6.116999999999997</v>
       </c>
       <c r="F48">
-        <v>36.294</v>
+        <v>37.08300000000001</v>
       </c>
       <c r="G48">
         <v>0.091</v>
@@ -5223,37 +5223,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M48">
-        <v>5.327959200000001</v>
+        <v>5.443784400000001</v>
       </c>
       <c r="N48">
-        <v>-0.5446258666666681</v>
+        <v>-0.6604510666666679</v>
       </c>
       <c r="O48">
-        <v>-0.136156466666667</v>
+        <v>-0.165112766666667</v>
       </c>
       <c r="P48">
-        <v>-0.4084694000000011</v>
+        <v>-0.4953383000000009</v>
       </c>
       <c r="Q48">
-        <v>3.021530599999999</v>
+        <v>2.934661699999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.190820182095492</v>
+        <v>0.1935564119463503</v>
       </c>
       <c r="T48">
-        <v>1.402455997235526</v>
+        <v>1.42891743114563</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2244449119154916</v>
+        <v>0.2196694882577152</v>
       </c>
       <c r="W48">
-        <v>0.1138514869308058</v>
+        <v>0.1145525191237674</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8977796476619664</v>
+        <v>0.8786779530308607</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1564245823197364</v>
+        <v>0.1574345823197364</v>
       </c>
       <c r="C49">
-        <v>28.7908940649863</v>
+        <v>27.40673151208366</v>
       </c>
       <c r="D49">
-        <v>65.78289406498631</v>
+        <v>65.18773151208367</v>
       </c>
       <c r="E49">
-        <v>-6.116999999999997</v>
+        <v>-5.327999999999996</v>
       </c>
       <c r="F49">
-        <v>37.08300000000001</v>
+        <v>37.87200000000001</v>
       </c>
       <c r="G49">
         <v>0.091</v>
@@ -5305,37 +5305,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M49">
-        <v>5.443784400000001</v>
+        <v>5.559609600000002</v>
       </c>
       <c r="N49">
-        <v>-0.6604510666666679</v>
+        <v>-0.7762762666666685</v>
       </c>
       <c r="O49">
-        <v>-0.165112766666667</v>
+        <v>-0.1940690666666671</v>
       </c>
       <c r="P49">
-        <v>-0.4953383000000009</v>
+        <v>-0.5822072000000014</v>
       </c>
       <c r="Q49">
-        <v>2.934661699999999</v>
+        <v>2.847792799999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1935564119463503</v>
+        <v>0.1963978814068571</v>
       </c>
       <c r="T49">
-        <v>1.42891743114563</v>
+        <v>1.456396612513815</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2196694882577152</v>
+        <v>0.2150930405856794</v>
       </c>
       <c r="W49">
-        <v>0.1145525191237674</v>
+        <v>0.1152243416420223</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8786779530308607</v>
+        <v>0.8603721623427176</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1574345823197364</v>
+        <v>0.1584445823197363</v>
       </c>
       <c r="C50">
-        <v>27.40673151208367</v>
+        <v>26.03324171709005</v>
       </c>
       <c r="D50">
-        <v>65.18773151208367</v>
+        <v>64.60324171709006</v>
       </c>
       <c r="E50">
-        <v>-5.328000000000003</v>
+        <v>-4.539000000000001</v>
       </c>
       <c r="F50">
-        <v>37.872</v>
+        <v>38.661</v>
       </c>
       <c r="G50">
         <v>0.091</v>
@@ -5387,37 +5387,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M50">
-        <v>5.559609600000001</v>
+        <v>5.675434800000001</v>
       </c>
       <c r="N50">
-        <v>-0.7762762666666676</v>
+        <v>-0.8921014666666673</v>
       </c>
       <c r="O50">
-        <v>-0.1940690666666669</v>
+        <v>-0.2230253666666668</v>
       </c>
       <c r="P50">
-        <v>-0.5822072000000007</v>
+        <v>-0.6690761000000005</v>
       </c>
       <c r="Q50">
-        <v>2.8477928</v>
+        <v>2.7609239</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1963978814068571</v>
+        <v>0.1993507810422856</v>
       </c>
       <c r="T50">
-        <v>1.456396612513815</v>
+        <v>1.484953408837616</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2150930405856795</v>
+        <v>0.2107033866961758</v>
       </c>
       <c r="W50">
-        <v>0.1152243416420223</v>
+        <v>0.1158687428330014</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8603721623427178</v>
+        <v>0.8428135467847032</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1584445823197363</v>
+        <v>0.1594545823197364</v>
       </c>
       <c r="C51">
-        <v>26.03324171709005</v>
+        <v>24.67014014720613</v>
       </c>
       <c r="D51">
-        <v>64.60324171709006</v>
+        <v>64.02914014720614</v>
       </c>
       <c r="E51">
-        <v>-4.539000000000001</v>
+        <v>-3.75</v>
       </c>
       <c r="F51">
-        <v>38.661</v>
+        <v>39.45</v>
       </c>
       <c r="G51">
         <v>0.091</v>
@@ -5469,37 +5469,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M51">
-        <v>5.675434800000001</v>
+        <v>5.791260000000001</v>
       </c>
       <c r="N51">
-        <v>-0.8921014666666673</v>
+        <v>-1.007926666666668</v>
       </c>
       <c r="O51">
-        <v>-0.2230253666666668</v>
+        <v>-0.251981666666667</v>
       </c>
       <c r="P51">
-        <v>-0.6690761000000005</v>
+        <v>-0.755945000000001</v>
       </c>
       <c r="Q51">
-        <v>2.7609239</v>
+        <v>2.674054999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1993507810422856</v>
+        <v>0.2024217966631313</v>
       </c>
       <c r="T51">
-        <v>1.484953408837616</v>
+        <v>1.514652477014368</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2107033866961758</v>
+        <v>0.2064893189622523</v>
       </c>
       <c r="W51">
-        <v>0.1158687428330014</v>
+        <v>0.1164873679763414</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8428135467847032</v>
+        <v>0.825957275849009</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1594545823197364</v>
+        <v>0.1604645823197364</v>
       </c>
       <c r="C52">
-        <v>24.67014014720613</v>
+        <v>23.31715229463322</v>
       </c>
       <c r="D52">
-        <v>64.02914014720614</v>
+        <v>63.46515229463322</v>
       </c>
       <c r="E52">
-        <v>-3.75</v>
+        <v>-2.960999999999999</v>
       </c>
       <c r="F52">
-        <v>39.45</v>
+        <v>40.239</v>
       </c>
       <c r="G52">
         <v>0.091</v>
@@ -5551,37 +5551,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M52">
-        <v>5.791260000000001</v>
+        <v>5.907085200000001</v>
       </c>
       <c r="N52">
-        <v>-1.007926666666668</v>
+        <v>-1.123751866666668</v>
       </c>
       <c r="O52">
-        <v>-0.251981666666667</v>
+        <v>-0.2809379666666669</v>
       </c>
       <c r="P52">
-        <v>-0.755945000000001</v>
+        <v>-0.8428139000000008</v>
       </c>
       <c r="Q52">
-        <v>2.674054999999999</v>
+        <v>2.587186099999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2024217966631313</v>
+        <v>0.2056181598603381</v>
       </c>
       <c r="T52">
-        <v>1.514652477014368</v>
+        <v>1.545563752055477</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2064893189622523</v>
+        <v>0.2024405087865218</v>
       </c>
       <c r="W52">
-        <v>0.1164873679763414</v>
+        <v>0.1170817333101386</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.825957275849009</v>
+        <v>0.8097620351460874</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1604645823197364</v>
+        <v>0.1919792145941229</v>
       </c>
       <c r="C53">
-        <v>23.31715229463322</v>
+        <v>8.845762890936705</v>
       </c>
       <c r="D53">
-        <v>63.46515229463322</v>
+        <v>49.78276289093671</v>
       </c>
       <c r="E53">
-        <v>-2.960999999999999</v>
+        <v>-2.171999999999997</v>
       </c>
       <c r="F53">
-        <v>40.239</v>
+        <v>41.02800000000001</v>
       </c>
       <c r="G53">
         <v>0.091</v>
@@ -5633,45 +5633,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M53">
-        <v>5.907085200000001</v>
+        <v>8.238422400000001</v>
       </c>
       <c r="N53">
-        <v>-1.123751866666668</v>
+        <v>-3.455089066666668</v>
       </c>
       <c r="O53">
-        <v>-0.2809379666666669</v>
+        <v>-0.863772266666667</v>
       </c>
       <c r="P53">
-        <v>-0.8428139000000008</v>
+        <v>-2.591316800000001</v>
       </c>
       <c r="Q53">
-        <v>2.587186099999999</v>
+        <v>0.8386831999999993</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2056181598603381</v>
+        <v>0.2139990220957338</v>
       </c>
       <c r="T53">
-        <v>1.545563752055477</v>
+        <v>1.626613095217217</v>
       </c>
       <c r="U53">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.2024405087865218</v>
+        <v>0.1451531950259473</v>
       </c>
       <c r="W53">
-        <v>0.1170817333101386</v>
+        <v>0.1716532384387898</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8097620351460874</v>
+        <v>0.5806127801037894</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1919792145941229</v>
+        <v>0.1935292145941229</v>
       </c>
       <c r="C54">
-        <v>8.845762890936705</v>
+        <v>7.534433690900315</v>
       </c>
       <c r="D54">
-        <v>49.78276289093671</v>
+        <v>49.26043369090032</v>
       </c>
       <c r="E54">
-        <v>-2.171999999999997</v>
+        <v>-1.382999999999996</v>
       </c>
       <c r="F54">
-        <v>41.02800000000001</v>
+        <v>41.81700000000001</v>
       </c>
       <c r="G54">
         <v>0.091</v>
@@ -5715,37 +5715,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M54">
-        <v>8.238422400000001</v>
+        <v>8.396853600000002</v>
       </c>
       <c r="N54">
-        <v>-3.455089066666668</v>
+        <v>-3.613520266666669</v>
       </c>
       <c r="O54">
-        <v>-0.863772266666667</v>
+        <v>-0.9033800666666671</v>
       </c>
       <c r="P54">
-        <v>-2.591316800000001</v>
+        <v>-2.710140200000001</v>
       </c>
       <c r="Q54">
-        <v>0.8386831999999993</v>
+        <v>0.7198597999999987</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2139990220957338</v>
+        <v>0.2175777246935154</v>
       </c>
       <c r="T54">
-        <v>1.626613095217217</v>
+        <v>1.661221884477158</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1451531950259473</v>
+        <v>0.1424144554971559</v>
       </c>
       <c r="W54">
-        <v>0.1716532384387898</v>
+        <v>0.1722031773361711</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5806127801037894</v>
+        <v>0.5696578219886235</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1935292145941229</v>
+        <v>0.1950792145941229</v>
       </c>
       <c r="C55">
-        <v>7.534433690900315</v>
+        <v>6.233951416368697</v>
       </c>
       <c r="D55">
-        <v>49.26043369090032</v>
+        <v>48.7489514163687</v>
       </c>
       <c r="E55">
-        <v>-1.382999999999996</v>
+        <v>-0.5939999999999941</v>
       </c>
       <c r="F55">
-        <v>41.81700000000001</v>
+        <v>42.60600000000001</v>
       </c>
       <c r="G55">
         <v>0.091</v>
@@ -5797,37 +5797,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M55">
-        <v>8.396853600000002</v>
+        <v>8.555284800000003</v>
       </c>
       <c r="N55">
-        <v>-3.613520266666669</v>
+        <v>-3.771951466666669</v>
       </c>
       <c r="O55">
-        <v>-0.9033800666666671</v>
+        <v>-0.9429878666666673</v>
       </c>
       <c r="P55">
-        <v>-2.710140200000001</v>
+        <v>-2.828963600000002</v>
       </c>
       <c r="Q55">
-        <v>0.7198597999999987</v>
+        <v>0.6010363999999981</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2175777246935154</v>
+        <v>0.2213120230564179</v>
       </c>
       <c r="T55">
-        <v>1.661221884477158</v>
+        <v>1.697335403704922</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1424144554971559</v>
+        <v>0.1397771507657271</v>
       </c>
       <c r="W55">
-        <v>0.1722031773361711</v>
+        <v>0.172732748126242</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5696578219886235</v>
+        <v>0.5591086030629082</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1950792145941229</v>
+        <v>0.1966292145941229</v>
       </c>
       <c r="C56">
-        <v>6.233951416368697</v>
+        <v>4.943981661280446</v>
       </c>
       <c r="D56">
-        <v>48.7489514163687</v>
+        <v>48.24798166128045</v>
       </c>
       <c r="E56">
-        <v>-0.5939999999999941</v>
+        <v>0.1950000000000003</v>
       </c>
       <c r="F56">
-        <v>42.60600000000001</v>
+        <v>43.395</v>
       </c>
       <c r="G56">
         <v>0.091</v>
@@ -5879,37 +5879,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M56">
-        <v>8.555284800000003</v>
+        <v>8.713716000000002</v>
       </c>
       <c r="N56">
-        <v>-3.771951466666669</v>
+        <v>-3.930382666666668</v>
       </c>
       <c r="O56">
-        <v>-0.9429878666666673</v>
+        <v>-0.9825956666666671</v>
       </c>
       <c r="P56">
-        <v>-2.828963600000002</v>
+        <v>-2.947787000000001</v>
       </c>
       <c r="Q56">
-        <v>0.6010363999999981</v>
+        <v>0.4822129999999989</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2213120230564179</v>
+        <v>0.2252122902354494</v>
       </c>
       <c r="T56">
-        <v>1.697335403704922</v>
+        <v>1.735053968231698</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1397771507657271</v>
+        <v>0.137235748024532</v>
       </c>
       <c r="W56">
-        <v>0.172732748126242</v>
+        <v>0.173243061796674</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5591086030629082</v>
+        <v>0.5489429920981281</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1966292145941229</v>
+        <v>0.1981792145941229</v>
       </c>
       <c r="C57">
-        <v>4.943981661280446</v>
+        <v>3.664203625875949</v>
       </c>
       <c r="D57">
-        <v>48.24798166128045</v>
+        <v>47.75720362587595</v>
       </c>
       <c r="E57">
-        <v>0.1950000000000003</v>
+        <v>0.9840000000000018</v>
       </c>
       <c r="F57">
-        <v>43.395</v>
+        <v>44.184</v>
       </c>
       <c r="G57">
         <v>0.091</v>
@@ -5961,37 +5961,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M57">
-        <v>8.713716000000002</v>
+        <v>8.872147200000001</v>
       </c>
       <c r="N57">
-        <v>-3.930382666666668</v>
+        <v>-4.088813866666667</v>
       </c>
       <c r="O57">
-        <v>-0.9825956666666671</v>
+        <v>-1.022203466666667</v>
       </c>
       <c r="P57">
-        <v>-2.947787000000001</v>
+        <v>-3.066610400000001</v>
       </c>
       <c r="Q57">
-        <v>0.4822129999999989</v>
+        <v>0.3633895999999996</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2252122902354494</v>
+        <v>0.2292898422862551</v>
       </c>
       <c r="T57">
-        <v>1.735053968231698</v>
+        <v>1.774487012964236</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.137235748024532</v>
+        <v>0.1347851096669511</v>
       </c>
       <c r="W57">
-        <v>0.173243061796674</v>
+        <v>0.1737351499788762</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5489429920981281</v>
+        <v>0.5391404386678045</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1981792145941229</v>
+        <v>0.1997292145941229</v>
       </c>
       <c r="C58">
-        <v>3.664203625875949</v>
+        <v>2.394309431649774</v>
       </c>
       <c r="D58">
-        <v>47.75720362587595</v>
+        <v>47.27630943164978</v>
       </c>
       <c r="E58">
-        <v>0.9840000000000018</v>
+        <v>1.773000000000003</v>
       </c>
       <c r="F58">
-        <v>44.184</v>
+        <v>44.97300000000001</v>
       </c>
       <c r="G58">
         <v>0.091</v>
@@ -6043,37 +6043,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M58">
-        <v>8.872147200000001</v>
+        <v>9.030578400000001</v>
       </c>
       <c r="N58">
-        <v>-4.088813866666667</v>
+        <v>-4.247245066666668</v>
       </c>
       <c r="O58">
-        <v>-1.022203466666667</v>
+        <v>-1.061811266666667</v>
       </c>
       <c r="P58">
-        <v>-3.066610400000001</v>
+        <v>-3.185433800000001</v>
       </c>
       <c r="Q58">
-        <v>0.3633895999999996</v>
+        <v>0.2445661999999991</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2292898422862551</v>
+        <v>0.2335570479208191</v>
       </c>
       <c r="T58">
-        <v>1.774487012964236</v>
+        <v>1.815754152800614</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1347851096669511</v>
+        <v>0.1324204586201625</v>
       </c>
       <c r="W58">
-        <v>0.1737351499788762</v>
+        <v>0.1742099719090714</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5391404386678045</v>
+        <v>0.52968183448065</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1997292145941229</v>
+        <v>0.2012792145941229</v>
       </c>
       <c r="C59">
-        <v>2.394309431649774</v>
+        <v>1.134003477279286</v>
       </c>
       <c r="D59">
-        <v>47.27630943164978</v>
+        <v>46.80500347727929</v>
       </c>
       <c r="E59">
-        <v>1.773000000000003</v>
+        <v>2.562000000000005</v>
       </c>
       <c r="F59">
-        <v>44.97300000000001</v>
+        <v>45.76200000000001</v>
       </c>
       <c r="G59">
         <v>0.091</v>
@@ -6125,37 +6125,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M59">
-        <v>9.030578400000001</v>
+        <v>9.189009600000002</v>
       </c>
       <c r="N59">
-        <v>-4.247245066666668</v>
+        <v>-4.405676266666669</v>
       </c>
       <c r="O59">
-        <v>-1.061811266666667</v>
+        <v>-1.101419066666667</v>
       </c>
       <c r="P59">
-        <v>-3.185433800000001</v>
+        <v>-3.304257200000002</v>
       </c>
       <c r="Q59">
-        <v>0.2445661999999991</v>
+        <v>0.1257427999999985</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2335570479208191</v>
+        <v>0.2380274538236958</v>
       </c>
       <c r="T59">
-        <v>1.815754152800614</v>
+        <v>1.858986394533962</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1324204586201625</v>
+        <v>0.1301373472646424</v>
       </c>
       <c r="W59">
-        <v>0.1742099719090714</v>
+        <v>0.1746684206692598</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.52968183448065</v>
+        <v>0.5205493890585697</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2012792145941229</v>
+        <v>0.2028292145941229</v>
       </c>
       <c r="C60">
-        <v>1.134003477279293</v>
+        <v>-0.1169981673019223</v>
       </c>
       <c r="D60">
-        <v>46.80500347727929</v>
+        <v>46.34300183269808</v>
       </c>
       <c r="E60">
-        <v>2.561999999999998</v>
+        <v>3.350999999999999</v>
       </c>
       <c r="F60">
-        <v>45.762</v>
+        <v>46.551</v>
       </c>
       <c r="G60">
         <v>0.091</v>
@@ -6207,37 +6207,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M60">
-        <v>9.1890096</v>
+        <v>9.347440800000001</v>
       </c>
       <c r="N60">
-        <v>-4.405676266666667</v>
+        <v>-4.564107466666668</v>
       </c>
       <c r="O60">
-        <v>-1.101419066666667</v>
+        <v>-1.141026866666667</v>
       </c>
       <c r="P60">
-        <v>-3.3042572</v>
+        <v>-3.423080600000001</v>
       </c>
       <c r="Q60">
-        <v>0.1257427999999998</v>
+        <v>0.006919399999999243</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2380274538236958</v>
+        <v>0.2427159283072005</v>
       </c>
       <c r="T60">
-        <v>1.858986394533962</v>
+        <v>1.90432752610796</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1301373472646425</v>
+        <v>0.1279316295143943</v>
       </c>
       <c r="W60">
-        <v>0.1746684206692598</v>
+        <v>0.1751113287935096</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5205493890585698</v>
+        <v>0.5117265180575771</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2028292145941229</v>
+        <v>0.2043792145941229</v>
       </c>
       <c r="C61">
-        <v>-0.1169981673019223</v>
+        <v>-1.358968331295571</v>
       </c>
       <c r="D61">
-        <v>46.34300183269808</v>
+        <v>45.89003166870443</v>
       </c>
       <c r="E61">
-        <v>3.350999999999999</v>
+        <v>4.140000000000001</v>
       </c>
       <c r="F61">
-        <v>46.551</v>
+        <v>47.34</v>
       </c>
       <c r="G61">
         <v>0.091</v>
@@ -6289,37 +6289,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M61">
-        <v>9.347440800000001</v>
+        <v>9.505872</v>
       </c>
       <c r="N61">
-        <v>-4.564107466666668</v>
+        <v>-4.722538666666667</v>
       </c>
       <c r="O61">
-        <v>-1.141026866666667</v>
+        <v>-1.180634666666667</v>
       </c>
       <c r="P61">
-        <v>-3.423080600000001</v>
+        <v>-3.541904</v>
       </c>
       <c r="Q61">
-        <v>0.006919399999999243</v>
+        <v>-0.111904</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2427159283072005</v>
+        <v>0.2476388265148805</v>
       </c>
       <c r="T61">
-        <v>1.90432752610796</v>
+        <v>1.951935714260659</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1279316295143943</v>
+        <v>0.1257994356891544</v>
       </c>
       <c r="W61">
-        <v>0.1751113287935096</v>
+        <v>0.1755394733136178</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5117265180575771</v>
+        <v>0.5031977427566174</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2043792145941229</v>
+        <v>0.228257583003148</v>
       </c>
       <c r="C62">
-        <v>-1.358968331295571</v>
+        <v>-8.153633124456007</v>
       </c>
       <c r="D62">
-        <v>45.89003166870443</v>
+        <v>39.884366875544</v>
       </c>
       <c r="E62">
-        <v>4.140000000000001</v>
+        <v>4.929000000000002</v>
       </c>
       <c r="F62">
-        <v>47.34</v>
+        <v>48.129</v>
       </c>
       <c r="G62">
         <v>0.091</v>
@@ -6371,45 +6371,45 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M62">
-        <v>9.505872</v>
+        <v>11.3488182</v>
       </c>
       <c r="N62">
-        <v>-4.722538666666667</v>
+        <v>-6.565484866666669</v>
       </c>
       <c r="O62">
-        <v>-1.180634666666667</v>
+        <v>-1.641371216666667</v>
       </c>
       <c r="P62">
-        <v>-3.541904</v>
+        <v>-4.924113650000002</v>
       </c>
       <c r="Q62">
-        <v>-0.111904</v>
+        <v>-1.494113650000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2476388265148805</v>
+        <v>0.2553228179871213</v>
       </c>
       <c r="T62">
-        <v>1.951935714260659</v>
+        <v>2.026245784536634</v>
       </c>
       <c r="U62">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1257994356891544</v>
+        <v>0.1053707366052734</v>
       </c>
       <c r="W62">
-        <v>0.1755394733136178</v>
+        <v>0.2109535803084766</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5031977427566174</v>
+        <v>0.4214829464210936</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.228257583003148</v>
+        <v>0.230157583003148</v>
       </c>
       <c r="C63">
-        <v>-8.153633124456007</v>
+        <v>-9.353683735063314</v>
       </c>
       <c r="D63">
-        <v>39.884366875544</v>
+        <v>39.47331626493669</v>
       </c>
       <c r="E63">
-        <v>4.929000000000002</v>
+        <v>5.718000000000004</v>
       </c>
       <c r="F63">
-        <v>48.129</v>
+        <v>48.91800000000001</v>
       </c>
       <c r="G63">
         <v>0.091</v>
@@ -6453,37 +6453,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M63">
-        <v>11.3488182</v>
+        <v>11.5348644</v>
       </c>
       <c r="N63">
-        <v>-6.565484866666669</v>
+        <v>-6.751531066666669</v>
       </c>
       <c r="O63">
-        <v>-1.641371216666667</v>
+        <v>-1.687882766666667</v>
       </c>
       <c r="P63">
-        <v>-4.924113650000002</v>
+        <v>-5.063648300000001</v>
       </c>
       <c r="Q63">
-        <v>-1.494113650000001</v>
+        <v>-1.633648300000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2553228179871213</v>
+        <v>0.2608365763552034</v>
       </c>
       <c r="T63">
-        <v>2.026245784536634</v>
+        <v>2.079568042024441</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1053707366052734</v>
+        <v>0.1036712085955109</v>
       </c>
       <c r="W63">
-        <v>0.2109535803084766</v>
+        <v>0.2113543290131785</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4214829464210936</v>
+        <v>0.4146848343820437</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.230157583003148</v>
+        <v>0.232057583003148</v>
       </c>
       <c r="C64">
-        <v>-9.353683735063314</v>
+        <v>-10.54534815115912</v>
       </c>
       <c r="D64">
-        <v>39.47331626493669</v>
+        <v>39.07065184884087</v>
       </c>
       <c r="E64">
-        <v>5.718000000000004</v>
+        <v>6.506999999999998</v>
       </c>
       <c r="F64">
-        <v>48.91800000000001</v>
+        <v>49.707</v>
       </c>
       <c r="G64">
         <v>0.091</v>
@@ -6535,37 +6535,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M64">
-        <v>11.5348644</v>
+        <v>11.7209106</v>
       </c>
       <c r="N64">
-        <v>-6.751531066666669</v>
+        <v>-6.937577266666667</v>
       </c>
       <c r="O64">
-        <v>-1.687882766666667</v>
+        <v>-1.734394316666667</v>
       </c>
       <c r="P64">
-        <v>-5.063648300000001</v>
+        <v>-5.20318295</v>
       </c>
       <c r="Q64">
-        <v>-1.633648300000001</v>
+        <v>-1.77318295</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2608365763552034</v>
+        <v>0.2666483757161549</v>
       </c>
       <c r="T64">
-        <v>2.079568042024441</v>
+        <v>2.135772583700777</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1036712085955109</v>
+        <v>0.1020256338558997</v>
       </c>
       <c r="W64">
-        <v>0.2113543290131785</v>
+        <v>0.2117423555367789</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4146848343820437</v>
+        <v>0.4081025354235986</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.232057583003148</v>
+        <v>0.233957583003148</v>
       </c>
       <c r="C65">
-        <v>-10.54534815115912</v>
+        <v>-11.72888042207779</v>
       </c>
       <c r="D65">
-        <v>39.07065184884087</v>
+        <v>38.67611957792221</v>
       </c>
       <c r="E65">
-        <v>6.506999999999998</v>
+        <v>7.295999999999999</v>
       </c>
       <c r="F65">
-        <v>49.707</v>
+        <v>50.496</v>
       </c>
       <c r="G65">
         <v>0.091</v>
@@ -6617,37 +6617,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M65">
-        <v>11.7209106</v>
+        <v>11.9069568</v>
       </c>
       <c r="N65">
-        <v>-6.937577266666667</v>
+        <v>-7.123623466666668</v>
       </c>
       <c r="O65">
-        <v>-1.734394316666667</v>
+        <v>-1.780905866666667</v>
       </c>
       <c r="P65">
-        <v>-5.20318295</v>
+        <v>-5.342717600000001</v>
       </c>
       <c r="Q65">
-        <v>-1.77318295</v>
+        <v>-1.912717600000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2666483757161549</v>
+        <v>0.2727830528193814</v>
       </c>
       <c r="T65">
-        <v>2.135772583700777</v>
+        <v>2.195099599914687</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1020256338558997</v>
+        <v>0.1004314833269012</v>
       </c>
       <c r="W65">
-        <v>0.2117423555367789</v>
+        <v>0.2121182562315167</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4081025354235986</v>
+        <v>0.4017259333076049</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.233957583003148</v>
+        <v>0.235857583003148</v>
       </c>
       <c r="C66">
-        <v>-11.72888042207779</v>
+        <v>-12.9045244382591</v>
       </c>
       <c r="D66">
-        <v>38.67611957792221</v>
+        <v>38.2894755617409</v>
       </c>
       <c r="E66">
-        <v>7.295999999999999</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="F66">
-        <v>50.496</v>
+        <v>51.285</v>
       </c>
       <c r="G66">
         <v>0.091</v>
@@ -6699,37 +6699,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M66">
-        <v>11.9069568</v>
+        <v>12.093003</v>
       </c>
       <c r="N66">
-        <v>-7.123623466666668</v>
+        <v>-7.309669666666668</v>
       </c>
       <c r="O66">
-        <v>-1.780905866666667</v>
+        <v>-1.827417416666667</v>
       </c>
       <c r="P66">
-        <v>-5.342717600000001</v>
+        <v>-5.482252250000001</v>
       </c>
       <c r="Q66">
-        <v>-1.912717600000001</v>
+        <v>-2.052252250000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2727830528193814</v>
+        <v>0.2792682828999351</v>
       </c>
       <c r="T66">
-        <v>2.195099599914687</v>
+        <v>2.257816731340821</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1004314833269012</v>
+        <v>0.09888638358341044</v>
       </c>
       <c r="W66">
-        <v>0.2121182562315167</v>
+        <v>0.2124825907510318</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4017259333076049</v>
+        <v>0.3955455343336417</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.235857583003148</v>
+        <v>0.237757583003148</v>
       </c>
       <c r="C67">
-        <v>-12.9045244382591</v>
+        <v>-14.07251443401309</v>
       </c>
       <c r="D67">
-        <v>38.2894755617409</v>
+        <v>37.91048556598692</v>
       </c>
       <c r="E67">
-        <v>8.085000000000001</v>
+        <v>8.874000000000002</v>
       </c>
       <c r="F67">
-        <v>51.285</v>
+        <v>52.07400000000001</v>
       </c>
       <c r="G67">
         <v>0.091</v>
@@ -6781,37 +6781,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M67">
-        <v>12.093003</v>
+        <v>12.2790492</v>
       </c>
       <c r="N67">
-        <v>-7.309669666666668</v>
+        <v>-7.495715866666668</v>
       </c>
       <c r="O67">
-        <v>-1.827417416666667</v>
+        <v>-1.873928966666667</v>
       </c>
       <c r="P67">
-        <v>-5.482252250000001</v>
+        <v>-5.621786900000001</v>
       </c>
       <c r="Q67">
-        <v>-2.052252250000001</v>
+        <v>-2.191786900000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2792682828999351</v>
+        <v>0.2861349971028744</v>
       </c>
       <c r="T67">
-        <v>2.257816731340821</v>
+        <v>2.324223105792022</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09888638358341044</v>
+        <v>0.09738810504426786</v>
       </c>
       <c r="W67">
-        <v>0.2124825907510318</v>
+        <v>0.2128358848305617</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3955455343336417</v>
+        <v>0.3895524201770715</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.237757583003148</v>
+        <v>0.239657583003148</v>
       </c>
       <c r="C68">
-        <v>-14.07251443401309</v>
+        <v>-15.233075460719</v>
       </c>
       <c r="D68">
-        <v>37.91048556598692</v>
+        <v>37.53892453928101</v>
       </c>
       <c r="E68">
-        <v>8.874000000000002</v>
+        <v>9.663000000000004</v>
       </c>
       <c r="F68">
-        <v>52.07400000000001</v>
+        <v>52.86300000000001</v>
       </c>
       <c r="G68">
         <v>0.091</v>
@@ -6863,37 +6863,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M68">
-        <v>12.2790492</v>
+        <v>12.4650954</v>
       </c>
       <c r="N68">
-        <v>-7.495715866666668</v>
+        <v>-7.681762066666669</v>
       </c>
       <c r="O68">
-        <v>-1.873928966666667</v>
+        <v>-1.920440516666667</v>
       </c>
       <c r="P68">
-        <v>-5.621786900000001</v>
+        <v>-5.761321550000002</v>
       </c>
       <c r="Q68">
-        <v>-2.191786900000001</v>
+        <v>-2.331321550000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2861349971028744</v>
+        <v>0.2934178758029615</v>
       </c>
       <c r="T68">
-        <v>2.324223105792022</v>
+        <v>2.394654108997841</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09738810504426786</v>
+        <v>0.09593455123763699</v>
       </c>
       <c r="W68">
-        <v>0.2128358848305617</v>
+        <v>0.2131786328181652</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3895524201770715</v>
+        <v>0.3837382049505479</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.239657583003148</v>
+        <v>0.241557583003148</v>
       </c>
       <c r="C69">
-        <v>-15.233075460719</v>
+        <v>-16.38642383246758</v>
       </c>
       <c r="D69">
-        <v>37.53892453928101</v>
+        <v>37.17457616753243</v>
       </c>
       <c r="E69">
-        <v>9.663000000000004</v>
+        <v>10.45200000000001</v>
       </c>
       <c r="F69">
-        <v>52.86300000000001</v>
+        <v>53.65200000000001</v>
       </c>
       <c r="G69">
         <v>0.091</v>
@@ -6945,37 +6945,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M69">
-        <v>12.4650954</v>
+        <v>12.6511416</v>
       </c>
       <c r="N69">
-        <v>-7.681762066666669</v>
+        <v>-7.867808266666669</v>
       </c>
       <c r="O69">
-        <v>-1.920440516666667</v>
+        <v>-1.966952066666667</v>
       </c>
       <c r="P69">
-        <v>-5.761321550000002</v>
+        <v>-5.900856200000002</v>
       </c>
       <c r="Q69">
-        <v>-2.331321550000002</v>
+        <v>-2.470856200000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2934178758029615</v>
+        <v>0.3011559344218041</v>
       </c>
       <c r="T69">
-        <v>2.394654108997841</v>
+        <v>2.469487049904024</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09593455123763699</v>
+        <v>0.09452374901355409</v>
       </c>
       <c r="W69">
-        <v>0.2131786328181652</v>
+        <v>0.213511299982604</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3837382049505479</v>
+        <v>0.3780949960542164</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.241557583003148</v>
+        <v>0.243457583003148</v>
       </c>
       <c r="C70">
-        <v>-16.38642383246758</v>
+        <v>-17.53276754600063</v>
       </c>
       <c r="D70">
-        <v>37.17457616753243</v>
+        <v>36.81723245399937</v>
       </c>
       <c r="E70">
-        <v>10.45200000000001</v>
+        <v>11.24100000000001</v>
       </c>
       <c r="F70">
-        <v>53.65200000000001</v>
+        <v>54.44100000000001</v>
       </c>
       <c r="G70">
         <v>0.091</v>
@@ -7027,37 +7027,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M70">
-        <v>12.6511416</v>
+        <v>12.8371878</v>
       </c>
       <c r="N70">
-        <v>-7.867808266666669</v>
+        <v>-8.053854466666669</v>
       </c>
       <c r="O70">
-        <v>-1.966952066666667</v>
+        <v>-2.013463616666667</v>
       </c>
       <c r="P70">
-        <v>-5.900856200000002</v>
+        <v>-6.040390850000001</v>
       </c>
       <c r="Q70">
-        <v>-2.470856200000001</v>
+        <v>-2.610390850000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3011559344218041</v>
+        <v>0.3093932226289591</v>
       </c>
       <c r="T70">
-        <v>2.469487049904024</v>
+        <v>2.549147922481573</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09452374901355409</v>
+        <v>0.09315383960756055</v>
       </c>
       <c r="W70">
-        <v>0.213511299982604</v>
+        <v>0.2138343246205372</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3780949960542164</v>
+        <v>0.3726153584302422</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.243457583003148</v>
+        <v>0.245357583003148</v>
       </c>
       <c r="C71">
-        <v>-17.53276754600063</v>
+        <v>-18.67230667666095</v>
       </c>
       <c r="D71">
-        <v>36.81723245399937</v>
+        <v>36.46669332333906</v>
       </c>
       <c r="E71">
-        <v>11.24100000000001</v>
+        <v>12.03000000000001</v>
       </c>
       <c r="F71">
-        <v>54.44100000000001</v>
+        <v>55.23000000000001</v>
       </c>
       <c r="G71">
         <v>0.091</v>
@@ -7109,37 +7109,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M71">
-        <v>12.8371878</v>
+        <v>13.023234</v>
       </c>
       <c r="N71">
-        <v>-8.053854466666669</v>
+        <v>-8.239900666666671</v>
       </c>
       <c r="O71">
-        <v>-2.013463616666667</v>
+        <v>-2.059975166666668</v>
       </c>
       <c r="P71">
-        <v>-6.040390850000001</v>
+        <v>-6.179925500000003</v>
       </c>
       <c r="Q71">
-        <v>-2.610390850000001</v>
+        <v>-2.749925500000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3093932226289591</v>
+        <v>0.3181796633832577</v>
       </c>
       <c r="T71">
-        <v>2.549147922481573</v>
+        <v>2.634119519897625</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09315383960756055</v>
+        <v>0.09182307047030967</v>
       </c>
       <c r="W71">
-        <v>0.2138343246205372</v>
+        <v>0.214148119983101</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3726153584302422</v>
+        <v>0.3672922818812387</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.245357583003148</v>
+        <v>0.247257583003148</v>
       </c>
       <c r="C72">
-        <v>-18.67230667666095</v>
+        <v>-19.80523375193647</v>
       </c>
       <c r="D72">
-        <v>36.46669332333906</v>
+        <v>36.12276624806354</v>
       </c>
       <c r="E72">
-        <v>12.03000000000001</v>
+        <v>12.81900000000001</v>
       </c>
       <c r="F72">
-        <v>55.23000000000001</v>
+        <v>56.01900000000001</v>
       </c>
       <c r="G72">
         <v>0.091</v>
@@ -7191,37 +7191,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M72">
-        <v>13.023234</v>
+        <v>13.2092802</v>
       </c>
       <c r="N72">
-        <v>-8.239900666666671</v>
+        <v>-8.425946866666671</v>
       </c>
       <c r="O72">
-        <v>-2.059975166666668</v>
+        <v>-2.106486716666668</v>
       </c>
       <c r="P72">
-        <v>-6.179925500000003</v>
+        <v>-6.319460150000003</v>
       </c>
       <c r="Q72">
-        <v>-2.749925500000003</v>
+        <v>-2.889460150000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3181796633832577</v>
+        <v>0.3275720655688873</v>
       </c>
       <c r="T72">
-        <v>2.634119519897625</v>
+        <v>2.724951227480302</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09182307047030967</v>
+        <v>0.09052978778762925</v>
       </c>
       <c r="W72">
-        <v>0.214148119983101</v>
+        <v>0.214453076039677</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3672922818812387</v>
+        <v>0.3621191511505171</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.247257583003148</v>
+        <v>0.249157583003148</v>
       </c>
       <c r="C73">
-        <v>-19.80523375193643</v>
+        <v>-20.93173410406375</v>
       </c>
       <c r="D73">
-        <v>36.12276624806356</v>
+        <v>35.78526589593625</v>
       </c>
       <c r="E73">
-        <v>12.819</v>
+        <v>13.608</v>
       </c>
       <c r="F73">
-        <v>56.019</v>
+        <v>56.808</v>
       </c>
       <c r="G73">
         <v>0.091</v>
@@ -7273,37 +7273,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M73">
-        <v>13.2092802</v>
+        <v>13.3953264</v>
       </c>
       <c r="N73">
-        <v>-8.425946866666667</v>
+        <v>-8.611993066666667</v>
       </c>
       <c r="O73">
-        <v>-2.106486716666667</v>
+        <v>-2.152998266666667</v>
       </c>
       <c r="P73">
-        <v>-6.31946015</v>
+        <v>-6.4589948</v>
       </c>
       <c r="Q73">
-        <v>-2.88946015</v>
+        <v>-3.0289948</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3275720655688872</v>
+        <v>0.3376353536249189</v>
       </c>
       <c r="T73">
-        <v>2.724951227480301</v>
+        <v>2.822270914176026</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09052978778762928</v>
+        <v>0.08927242962391221</v>
       </c>
       <c r="W73">
-        <v>0.214453076039677</v>
+        <v>0.2147495610946815</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3621191511505172</v>
+        <v>0.3570897184956489</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.249157583003148</v>
+        <v>0.251057583003148</v>
       </c>
       <c r="C74">
-        <v>-20.93173410406375</v>
+        <v>-22.05198620304825</v>
       </c>
       <c r="D74">
-        <v>35.78526589593625</v>
+        <v>35.45401379695175</v>
       </c>
       <c r="E74">
-        <v>13.608</v>
+        <v>14.397</v>
       </c>
       <c r="F74">
-        <v>56.808</v>
+        <v>57.597</v>
       </c>
       <c r="G74">
         <v>0.091</v>
@@ -7355,37 +7355,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M74">
-        <v>13.3953264</v>
+        <v>13.5813726</v>
       </c>
       <c r="N74">
-        <v>-8.611993066666667</v>
+        <v>-8.798039266666668</v>
       </c>
       <c r="O74">
-        <v>-2.152998266666667</v>
+        <v>-2.199509816666667</v>
       </c>
       <c r="P74">
-        <v>-6.4589948</v>
+        <v>-6.598529450000001</v>
       </c>
       <c r="Q74">
-        <v>-3.0289948</v>
+        <v>-3.168529450000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3376353536249189</v>
+        <v>0.3484440704258418</v>
       </c>
       <c r="T74">
-        <v>2.822270914176026</v>
+        <v>2.926799466552916</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08927242962391221</v>
+        <v>0.08804951962906409</v>
       </c>
       <c r="W74">
-        <v>0.2147495610946815</v>
+        <v>0.2150379232714667</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3570897184956489</v>
+        <v>0.3521980785162564</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.251057583003148</v>
+        <v>0.252957583003148</v>
       </c>
       <c r="C75">
-        <v>-22.05198620304825</v>
+        <v>-23.16616197135785</v>
       </c>
       <c r="D75">
-        <v>35.45401379695175</v>
+        <v>35.12883802864215</v>
       </c>
       <c r="E75">
-        <v>14.397</v>
+        <v>15.186</v>
       </c>
       <c r="F75">
-        <v>57.597</v>
+        <v>58.386</v>
       </c>
       <c r="G75">
         <v>0.091</v>
@@ -7437,37 +7437,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M75">
-        <v>13.5813726</v>
+        <v>13.7674188</v>
       </c>
       <c r="N75">
-        <v>-8.798039266666668</v>
+        <v>-8.984085466666668</v>
       </c>
       <c r="O75">
-        <v>-2.199509816666667</v>
+        <v>-2.246021366666667</v>
       </c>
       <c r="P75">
-        <v>-6.598529450000001</v>
+        <v>-6.738064100000001</v>
       </c>
       <c r="Q75">
-        <v>-3.168529450000001</v>
+        <v>-3.308064100000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3484440704258418</v>
+        <v>0.3600842269806819</v>
       </c>
       <c r="T75">
-        <v>2.926799466552916</v>
+        <v>3.039368676804951</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08804951962906409</v>
+        <v>0.08685966125569836</v>
       </c>
       <c r="W75">
-        <v>0.2150379232714667</v>
+        <v>0.2153184918759063</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3521980785162564</v>
+        <v>0.3474386450227934</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.252957583003148</v>
+        <v>0.254857583003148</v>
       </c>
       <c r="C76">
-        <v>-23.16616197135785</v>
+        <v>-24.27442708145633</v>
       </c>
       <c r="D76">
-        <v>35.12883802864215</v>
+        <v>34.80957291854367</v>
       </c>
       <c r="E76">
-        <v>15.186</v>
+        <v>15.975</v>
       </c>
       <c r="F76">
-        <v>58.386</v>
+        <v>59.175</v>
       </c>
       <c r="G76">
         <v>0.091</v>
@@ -7519,37 +7519,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M76">
-        <v>13.7674188</v>
+        <v>13.953465</v>
       </c>
       <c r="N76">
-        <v>-8.984085466666668</v>
+        <v>-9.170131666666668</v>
       </c>
       <c r="O76">
-        <v>-2.246021366666667</v>
+        <v>-2.292532916666667</v>
       </c>
       <c r="P76">
-        <v>-6.738064100000001</v>
+        <v>-6.877598750000001</v>
       </c>
       <c r="Q76">
-        <v>-3.308064100000001</v>
+        <v>-3.44759875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3600842269806819</v>
+        <v>0.3726555960599092</v>
       </c>
       <c r="T76">
-        <v>3.039368676804951</v>
+        <v>3.16094342387715</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08685966125569836</v>
+        <v>0.08570153243895572</v>
       </c>
       <c r="W76">
-        <v>0.2153184918759063</v>
+        <v>0.2155915786508943</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3474386450227934</v>
+        <v>0.3428061297558228</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.254857583003148</v>
+        <v>0.256757583003148</v>
       </c>
       <c r="C77">
-        <v>-24.27442708145633</v>
+        <v>-25.37694123725819</v>
       </c>
       <c r="D77">
-        <v>34.80957291854367</v>
+        <v>34.49605876274181</v>
       </c>
       <c r="E77">
-        <v>15.975</v>
+        <v>16.764</v>
       </c>
       <c r="F77">
-        <v>59.175</v>
+        <v>59.96400000000001</v>
       </c>
       <c r="G77">
         <v>0.091</v>
@@ -7601,37 +7601,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M77">
-        <v>13.953465</v>
+        <v>14.1395112</v>
       </c>
       <c r="N77">
-        <v>-9.170131666666668</v>
+        <v>-9.356177866666668</v>
       </c>
       <c r="O77">
-        <v>-2.292532916666667</v>
+        <v>-2.339044466666667</v>
       </c>
       <c r="P77">
-        <v>-6.877598750000001</v>
+        <v>-7.017133400000001</v>
       </c>
       <c r="Q77">
-        <v>-3.44759875</v>
+        <v>-3.5871334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3726555960599092</v>
+        <v>0.3862745792290721</v>
       </c>
       <c r="T77">
-        <v>3.16094342387715</v>
+        <v>3.292649399872031</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08570153243895572</v>
+        <v>0.08457388069633788</v>
       </c>
       <c r="W77">
-        <v>0.2155915786508943</v>
+        <v>0.2158574789318035</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3428061297558228</v>
+        <v>0.3382955227853515</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.256757583003148</v>
+        <v>0.258657583003148</v>
       </c>
       <c r="C78">
-        <v>-25.37694123725819</v>
+        <v>-26.47385844050973</v>
       </c>
       <c r="D78">
-        <v>34.49605876274181</v>
+        <v>34.18814155949028</v>
       </c>
       <c r="E78">
-        <v>16.764</v>
+        <v>17.553</v>
       </c>
       <c r="F78">
-        <v>59.96400000000001</v>
+        <v>60.75300000000001</v>
       </c>
       <c r="G78">
         <v>0.091</v>
@@ -7683,37 +7683,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M78">
-        <v>14.1395112</v>
+        <v>14.3255574</v>
       </c>
       <c r="N78">
-        <v>-9.356177866666668</v>
+        <v>-9.54222406666667</v>
       </c>
       <c r="O78">
-        <v>-2.339044466666667</v>
+        <v>-2.385556016666667</v>
       </c>
       <c r="P78">
-        <v>-7.017133400000001</v>
+        <v>-7.156668050000002</v>
       </c>
       <c r="Q78">
-        <v>-3.5871334</v>
+        <v>-3.726668050000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3862745792290721</v>
+        <v>0.4010778218042491</v>
       </c>
       <c r="T78">
-        <v>3.292649399872031</v>
+        <v>3.435808069431685</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08457388069633788</v>
+        <v>0.08347551860937244</v>
       </c>
       <c r="W78">
-        <v>0.2158574789318035</v>
+        <v>0.21611647271191</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3382955227853515</v>
+        <v>0.3339020744374898</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.258657583003148</v>
+        <v>0.260557583003148</v>
       </c>
       <c r="C79">
-        <v>-26.47385844050973</v>
+        <v>-27.56532724302963</v>
       </c>
       <c r="D79">
-        <v>34.18814155949028</v>
+        <v>33.88567275697038</v>
       </c>
       <c r="E79">
-        <v>17.553</v>
+        <v>18.34200000000001</v>
       </c>
       <c r="F79">
-        <v>60.75300000000001</v>
+        <v>61.54200000000001</v>
       </c>
       <c r="G79">
         <v>0.091</v>
@@ -7765,37 +7765,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M79">
-        <v>14.3255574</v>
+        <v>14.5116036</v>
       </c>
       <c r="N79">
-        <v>-9.54222406666667</v>
+        <v>-9.728270266666669</v>
       </c>
       <c r="O79">
-        <v>-2.385556016666667</v>
+        <v>-2.432067566666667</v>
       </c>
       <c r="P79">
-        <v>-7.156668050000002</v>
+        <v>-7.296202700000002</v>
       </c>
       <c r="Q79">
-        <v>-3.726668050000002</v>
+        <v>-3.866202700000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4010778218042491</v>
+        <v>0.4172268137044423</v>
       </c>
       <c r="T79">
-        <v>3.435808069431685</v>
+        <v>3.591981163496761</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08347551860937244</v>
+        <v>0.08240531965284202</v>
       </c>
       <c r="W79">
-        <v>0.21611647271191</v>
+        <v>0.2163688256258599</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3339020744374898</v>
+        <v>0.3296212786113681</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.260557583003148</v>
+        <v>0.262457583003148</v>
       </c>
       <c r="C80">
-        <v>-27.56532724302963</v>
+        <v>-28.65149098567743</v>
       </c>
       <c r="D80">
-        <v>33.88567275697038</v>
+        <v>33.58850901432258</v>
       </c>
       <c r="E80">
-        <v>18.34200000000001</v>
+        <v>19.13100000000001</v>
       </c>
       <c r="F80">
-        <v>61.54200000000001</v>
+        <v>62.33100000000001</v>
       </c>
       <c r="G80">
         <v>0.091</v>
@@ -7847,37 +7847,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M80">
-        <v>14.5116036</v>
+        <v>14.6976498</v>
       </c>
       <c r="N80">
-        <v>-9.728270266666669</v>
+        <v>-9.914316466666669</v>
       </c>
       <c r="O80">
-        <v>-2.432067566666667</v>
+        <v>-2.478579116666667</v>
       </c>
       <c r="P80">
-        <v>-7.296202700000002</v>
+        <v>-7.435737350000002</v>
       </c>
       <c r="Q80">
-        <v>-3.866202700000002</v>
+        <v>-4.005737350000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4172268137044423</v>
+        <v>0.4349138048332252</v>
       </c>
       <c r="T80">
-        <v>3.591981163496761</v>
+        <v>3.763027885568035</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08240531965284202</v>
+        <v>0.08136221434078074</v>
       </c>
       <c r="W80">
-        <v>0.2163688256258599</v>
+        <v>0.2166147898584439</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3296212786113681</v>
+        <v>0.3254488573631229</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.262457583003148</v>
+        <v>0.264357583003148</v>
       </c>
       <c r="C81">
-        <v>-28.65149098567743</v>
+        <v>-29.73248802485724</v>
       </c>
       <c r="D81">
-        <v>33.58850901432258</v>
+        <v>33.29651197514276</v>
       </c>
       <c r="E81">
-        <v>19.13100000000001</v>
+        <v>19.92</v>
       </c>
       <c r="F81">
-        <v>62.33100000000001</v>
+        <v>63.12</v>
       </c>
       <c r="G81">
         <v>0.091</v>
@@ -7929,37 +7929,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M81">
-        <v>14.6976498</v>
+        <v>14.883696</v>
       </c>
       <c r="N81">
-        <v>-9.914316466666669</v>
+        <v>-10.10036266666667</v>
       </c>
       <c r="O81">
-        <v>-2.478579116666667</v>
+        <v>-2.525090666666667</v>
       </c>
       <c r="P81">
-        <v>-7.435737350000002</v>
+        <v>-7.575272000000002</v>
       </c>
       <c r="Q81">
-        <v>-4.005737350000002</v>
+        <v>-4.145272000000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4349138048332252</v>
+        <v>0.4543694950748866</v>
       </c>
       <c r="T81">
-        <v>3.763027885568035</v>
+        <v>3.951179279846438</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08136221434078074</v>
+        <v>0.08034518666152098</v>
       </c>
       <c r="W81">
-        <v>0.2166147898584439</v>
+        <v>0.2168546049852134</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3254488573631229</v>
+        <v>0.321380746646084</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.264357583003148</v>
+        <v>0.2662575830031479</v>
       </c>
       <c r="C82">
-        <v>-29.73248802485724</v>
+        <v>-30.80845194730878</v>
       </c>
       <c r="D82">
-        <v>33.29651197514276</v>
+        <v>33.00954805269122</v>
       </c>
       <c r="E82">
-        <v>19.92</v>
+        <v>20.709</v>
       </c>
       <c r="F82">
-        <v>63.12</v>
+        <v>63.90900000000001</v>
       </c>
       <c r="G82">
         <v>0.091</v>
@@ -8011,37 +8011,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M82">
-        <v>14.883696</v>
+        <v>15.0697422</v>
       </c>
       <c r="N82">
-        <v>-10.10036266666667</v>
+        <v>-10.28640886666667</v>
       </c>
       <c r="O82">
-        <v>-2.525090666666667</v>
+        <v>-2.571602216666667</v>
       </c>
       <c r="P82">
-        <v>-7.575272000000002</v>
+        <v>-7.714806650000002</v>
       </c>
       <c r="Q82">
-        <v>-4.145272000000002</v>
+        <v>-4.284806650000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4543694950748866</v>
+        <v>0.4758731527104069</v>
       </c>
       <c r="T82">
-        <v>3.951179279846438</v>
+        <v>4.159136084048882</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08034518666152098</v>
+        <v>0.07935327077681084</v>
       </c>
       <c r="W82">
-        <v>0.2168546049852134</v>
+        <v>0.217088498750828</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.321380746646084</v>
+        <v>0.3174130831072434</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2662575830031479</v>
+        <v>0.268157583003148</v>
       </c>
       <c r="C83">
-        <v>-30.80845194730878</v>
+        <v>-31.87951177388653</v>
       </c>
       <c r="D83">
-        <v>33.00954805269122</v>
+        <v>32.72748822611347</v>
       </c>
       <c r="E83">
-        <v>20.709</v>
+        <v>21.498</v>
       </c>
       <c r="F83">
-        <v>63.90900000000001</v>
+        <v>64.69800000000001</v>
       </c>
       <c r="G83">
         <v>0.091</v>
@@ -8093,37 +8093,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M83">
-        <v>15.0697422</v>
+        <v>15.2557884</v>
       </c>
       <c r="N83">
-        <v>-10.28640886666667</v>
+        <v>-10.47245506666667</v>
       </c>
       <c r="O83">
-        <v>-2.571602216666667</v>
+        <v>-2.618113766666667</v>
       </c>
       <c r="P83">
-        <v>-7.714806650000002</v>
+        <v>-7.854341300000002</v>
       </c>
       <c r="Q83">
-        <v>-4.284806650000002</v>
+        <v>-4.424341300000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4758731527104069</v>
+        <v>0.4997661056387629</v>
       </c>
       <c r="T83">
-        <v>4.159136084048882</v>
+        <v>4.390199199829376</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07935327077681084</v>
+        <v>0.07838554796245949</v>
       </c>
       <c r="W83">
-        <v>0.217088498750828</v>
+        <v>0.2173166877904521</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3174130831072434</v>
+        <v>0.313542191849838</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.268157583003148</v>
+        <v>0.270057583003148</v>
       </c>
       <c r="C84">
-        <v>-31.87951177388653</v>
+        <v>-32.94579215297963</v>
       </c>
       <c r="D84">
-        <v>32.72748822611347</v>
+        <v>32.45020784702038</v>
       </c>
       <c r="E84">
-        <v>21.498</v>
+        <v>22.28700000000001</v>
       </c>
       <c r="F84">
-        <v>64.69800000000001</v>
+        <v>65.48700000000001</v>
       </c>
       <c r="G84">
         <v>0.091</v>
@@ -8175,37 +8175,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M84">
-        <v>15.2557884</v>
+        <v>15.4418346</v>
       </c>
       <c r="N84">
-        <v>-10.47245506666667</v>
+        <v>-10.65850126666667</v>
       </c>
       <c r="O84">
-        <v>-2.618113766666667</v>
+        <v>-2.664625316666668</v>
       </c>
       <c r="P84">
-        <v>-7.854341300000002</v>
+        <v>-7.993875950000003</v>
       </c>
       <c r="Q84">
-        <v>-4.424341300000002</v>
+        <v>-4.563875950000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4997661056387629</v>
+        <v>0.526469994205749</v>
       </c>
       <c r="T84">
-        <v>4.390199199829376</v>
+        <v>4.648446211584046</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07838554796245949</v>
+        <v>0.07744114377014069</v>
       </c>
       <c r="W84">
-        <v>0.2173166877904521</v>
+        <v>0.2175393782990008</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.313542191849838</v>
+        <v>0.3097645750805628</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.270057583003148</v>
+        <v>0.271957583003148</v>
       </c>
       <c r="C85">
-        <v>-32.94579215297963</v>
+        <v>-34.00741354418225</v>
       </c>
       <c r="D85">
-        <v>32.45020784702038</v>
+        <v>32.17758645581776</v>
       </c>
       <c r="E85">
-        <v>22.28700000000001</v>
+        <v>23.07600000000001</v>
       </c>
       <c r="F85">
-        <v>65.48700000000001</v>
+        <v>66.27600000000001</v>
       </c>
       <c r="G85">
         <v>0.091</v>
@@ -8257,37 +8257,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M85">
-        <v>15.4418346</v>
+        <v>15.6278808</v>
       </c>
       <c r="N85">
-        <v>-10.65850126666667</v>
+        <v>-10.84454746666667</v>
       </c>
       <c r="O85">
-        <v>-2.664625316666668</v>
+        <v>-2.711136866666668</v>
       </c>
       <c r="P85">
-        <v>-7.993875950000003</v>
+        <v>-8.133410600000003</v>
       </c>
       <c r="Q85">
-        <v>-4.563875950000003</v>
+        <v>-4.703410600000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.526469994205749</v>
+        <v>0.5565118688436084</v>
       </c>
       <c r="T85">
-        <v>4.648446211584046</v>
+        <v>4.93897409980805</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07744114377014069</v>
+        <v>0.07651922539192474</v>
       </c>
       <c r="W85">
-        <v>0.2175393782990008</v>
+        <v>0.2177567666525842</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3097645750805628</v>
+        <v>0.306076901567699</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.271957583003148</v>
+        <v>0.273857583003148</v>
       </c>
       <c r="C86">
-        <v>-34.00741354418223</v>
+        <v>-35.06449239278255</v>
       </c>
       <c r="D86">
-        <v>32.17758645581777</v>
+        <v>31.90950760721745</v>
       </c>
       <c r="E86">
-        <v>23.07599999999999</v>
+        <v>23.86499999999999</v>
       </c>
       <c r="F86">
-        <v>66.276</v>
+        <v>67.065</v>
       </c>
       <c r="G86">
         <v>0.091</v>
@@ -8339,37 +8339,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M86">
-        <v>15.6278808</v>
+        <v>15.813927</v>
       </c>
       <c r="N86">
-        <v>-10.84454746666667</v>
+        <v>-11.03059366666667</v>
       </c>
       <c r="O86">
-        <v>-2.711136866666667</v>
+        <v>-2.757648416666667</v>
       </c>
       <c r="P86">
-        <v>-8.133410599999999</v>
+        <v>-8.272945249999999</v>
       </c>
       <c r="Q86">
-        <v>-4.7034106</v>
+        <v>-4.84294525</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5565118688436079</v>
+        <v>0.5905593267665152</v>
       </c>
       <c r="T86">
-        <v>4.938974099808045</v>
+        <v>5.268239039795249</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07651922539192475</v>
+        <v>0.07561899921084328</v>
       </c>
       <c r="W86">
-        <v>0.2177567666525841</v>
+        <v>0.2179690399860832</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.306076901567699</v>
+        <v>0.3024759968433731</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.273857583003148</v>
+        <v>0.275757583003148</v>
       </c>
       <c r="C87">
-        <v>-35.06449239278255</v>
+        <v>-36.11714129560165</v>
       </c>
       <c r="D87">
-        <v>31.90950760721745</v>
+        <v>31.64585870439835</v>
       </c>
       <c r="E87">
-        <v>23.86499999999999</v>
+        <v>24.654</v>
       </c>
       <c r="F87">
-        <v>67.065</v>
+        <v>67.854</v>
       </c>
       <c r="G87">
         <v>0.091</v>
@@ -8421,37 +8421,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M87">
-        <v>15.813927</v>
+        <v>15.9999732</v>
       </c>
       <c r="N87">
-        <v>-11.03059366666667</v>
+        <v>-11.21663986666667</v>
       </c>
       <c r="O87">
-        <v>-2.757648416666667</v>
+        <v>-2.804159966666667</v>
       </c>
       <c r="P87">
-        <v>-8.272945249999999</v>
+        <v>-8.412479900000001</v>
       </c>
       <c r="Q87">
-        <v>-4.84294525</v>
+        <v>-4.982479900000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5905593267665152</v>
+        <v>0.6294707072498378</v>
       </c>
       <c r="T87">
-        <v>5.268239039795249</v>
+        <v>5.644541828352053</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07561899921084328</v>
+        <v>0.0747397085223451</v>
       </c>
       <c r="W87">
-        <v>0.2179690399860832</v>
+        <v>0.218176376730431</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3024759968433731</v>
+        <v>0.2989588340893804</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.275757583003148</v>
+        <v>0.277657583003148</v>
       </c>
       <c r="C88">
-        <v>-36.11714129560165</v>
+        <v>-37.16546915867844</v>
       </c>
       <c r="D88">
-        <v>31.64585870439835</v>
+        <v>31.38653084132156</v>
       </c>
       <c r="E88">
-        <v>24.654</v>
+        <v>25.443</v>
       </c>
       <c r="F88">
-        <v>67.854</v>
+        <v>68.643</v>
       </c>
       <c r="G88">
         <v>0.091</v>
@@ -8503,37 +8503,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M88">
-        <v>15.9999732</v>
+        <v>16.1860194</v>
       </c>
       <c r="N88">
-        <v>-11.21663986666667</v>
+        <v>-11.40268606666667</v>
       </c>
       <c r="O88">
-        <v>-2.804159966666667</v>
+        <v>-2.850671516666667</v>
       </c>
       <c r="P88">
-        <v>-8.412479900000001</v>
+        <v>-8.552014549999999</v>
       </c>
       <c r="Q88">
-        <v>-4.982479900000001</v>
+        <v>-5.122014549999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6294707072498378</v>
+        <v>0.6743684539613637</v>
       </c>
       <c r="T88">
-        <v>5.644541828352053</v>
+        <v>6.078737353609903</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0747397085223451</v>
+        <v>0.07388063141289286</v>
       </c>
       <c r="W88">
-        <v>0.218176376730431</v>
+        <v>0.2183789471128399</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2989588340893804</v>
+        <v>0.2955225256515714</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.277657583003148</v>
+        <v>0.279557583003148</v>
       </c>
       <c r="C89">
-        <v>-37.16546915867844</v>
+        <v>-38.20958134726446</v>
       </c>
       <c r="D89">
-        <v>31.38653084132156</v>
+        <v>31.13141865273554</v>
       </c>
       <c r="E89">
-        <v>25.443</v>
+        <v>26.232</v>
       </c>
       <c r="F89">
-        <v>68.643</v>
+        <v>69.432</v>
       </c>
       <c r="G89">
         <v>0.091</v>
@@ -8585,37 +8585,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M89">
-        <v>16.1860194</v>
+        <v>16.3720656</v>
       </c>
       <c r="N89">
-        <v>-11.40268606666667</v>
+        <v>-11.58873226666667</v>
       </c>
       <c r="O89">
-        <v>-2.850671516666667</v>
+        <v>-2.897183066666667</v>
       </c>
       <c r="P89">
-        <v>-8.552014549999999</v>
+        <v>-8.691549200000003</v>
       </c>
       <c r="Q89">
-        <v>-5.122014549999999</v>
+        <v>-5.261549200000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6743684539613637</v>
+        <v>0.7267491584581441</v>
       </c>
       <c r="T89">
-        <v>6.078737353609903</v>
+        <v>6.585298799744062</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07388063141289286</v>
+        <v>0.07304107878320089</v>
       </c>
       <c r="W89">
-        <v>0.2183789471128399</v>
+        <v>0.2185769136229213</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2955225256515714</v>
+        <v>0.2921643151328035</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.279557583003148</v>
+        <v>0.2814575830031479</v>
       </c>
       <c r="C90">
-        <v>-38.20958134726446</v>
+        <v>-39.24957982856267</v>
       </c>
       <c r="D90">
-        <v>31.13141865273554</v>
+        <v>30.88042017143733</v>
       </c>
       <c r="E90">
-        <v>26.232</v>
+        <v>27.021</v>
       </c>
       <c r="F90">
-        <v>69.432</v>
+        <v>70.221</v>
       </c>
       <c r="G90">
         <v>0.091</v>
@@ -8667,37 +8667,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M90">
-        <v>16.3720656</v>
+        <v>16.5581118</v>
       </c>
       <c r="N90">
-        <v>-11.58873226666667</v>
+        <v>-11.77477846666667</v>
       </c>
       <c r="O90">
-        <v>-2.897183066666667</v>
+        <v>-2.943694616666667</v>
       </c>
       <c r="P90">
-        <v>-8.691549200000003</v>
+        <v>-8.831083850000002</v>
       </c>
       <c r="Q90">
-        <v>-5.261549200000003</v>
+        <v>-5.401083850000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7267491584581441</v>
+        <v>0.7886536274088845</v>
       </c>
       <c r="T90">
-        <v>6.585298799744062</v>
+        <v>7.183962326993522</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07304107878320089</v>
+        <v>0.07222039250473795</v>
       </c>
       <c r="W90">
-        <v>0.2185769136229213</v>
+        <v>0.2187704314473828</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2921643151328035</v>
+        <v>0.2888815700189519</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2814575830031479</v>
+        <v>0.283357583003148</v>
       </c>
       <c r="C91">
-        <v>-39.24957982856267</v>
+        <v>-40.28556330761648</v>
       </c>
       <c r="D91">
-        <v>30.88042017143733</v>
+        <v>30.63343669238352</v>
       </c>
       <c r="E91">
-        <v>27.021</v>
+        <v>27.81</v>
       </c>
       <c r="F91">
-        <v>70.221</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="G91">
         <v>0.091</v>
@@ -8749,37 +8749,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M91">
-        <v>16.5581118</v>
+        <v>16.744158</v>
       </c>
       <c r="N91">
-        <v>-11.77477846666667</v>
+        <v>-11.96082466666667</v>
       </c>
       <c r="O91">
-        <v>-2.943694616666667</v>
+        <v>-2.990206166666667</v>
       </c>
       <c r="P91">
-        <v>-8.831083850000002</v>
+        <v>-8.970618500000002</v>
       </c>
       <c r="Q91">
-        <v>-5.401083850000003</v>
+        <v>-5.540618500000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7886536274088845</v>
+        <v>0.862938990149773</v>
       </c>
       <c r="T91">
-        <v>7.183962326993522</v>
+        <v>7.902358559692876</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07222039250473795</v>
+        <v>0.07141794369912975</v>
       </c>
       <c r="W91">
-        <v>0.2187704314473828</v>
+        <v>0.2189596488757452</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2888815700189519</v>
+        <v>0.2856717747965191</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.283357583003148</v>
+        <v>0.285257583003148</v>
       </c>
       <c r="C92">
-        <v>-40.28556330761648</v>
+        <v>-41.31762735672937</v>
       </c>
       <c r="D92">
-        <v>30.63343669238352</v>
+        <v>30.39037264327064</v>
       </c>
       <c r="E92">
-        <v>27.81</v>
+        <v>28.599</v>
       </c>
       <c r="F92">
-        <v>71.01000000000001</v>
+        <v>71.79900000000001</v>
       </c>
       <c r="G92">
         <v>0.091</v>
@@ -8831,37 +8831,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M92">
-        <v>16.744158</v>
+        <v>16.9302042</v>
       </c>
       <c r="N92">
-        <v>-11.96082466666667</v>
+        <v>-12.14687086666667</v>
       </c>
       <c r="O92">
-        <v>-2.990206166666667</v>
+        <v>-3.036717716666667</v>
       </c>
       <c r="P92">
-        <v>-8.970618500000002</v>
+        <v>-9.110153150000002</v>
       </c>
       <c r="Q92">
-        <v>-5.540618500000003</v>
+        <v>-5.680153150000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.862938990149773</v>
+        <v>0.9537322112775258</v>
       </c>
       <c r="T92">
-        <v>7.902358559692876</v>
+        <v>8.780398399658752</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07141794369912975</v>
+        <v>0.07063313113100746</v>
       </c>
       <c r="W92">
-        <v>0.2189596488757452</v>
+        <v>0.2191447076793085</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2856717747965191</v>
+        <v>0.2825325245240298</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.285257583003148</v>
+        <v>0.287157583003148</v>
       </c>
       <c r="C93">
-        <v>-41.31762735672937</v>
+        <v>-42.34586453877167</v>
       </c>
       <c r="D93">
-        <v>30.39037264327064</v>
+        <v>30.15113546122834</v>
       </c>
       <c r="E93">
-        <v>28.599</v>
+        <v>29.38800000000001</v>
       </c>
       <c r="F93">
-        <v>71.79900000000001</v>
+        <v>72.58800000000001</v>
       </c>
       <c r="G93">
         <v>0.091</v>
@@ -8913,37 +8913,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M93">
-        <v>16.9302042</v>
+        <v>17.1162504</v>
       </c>
       <c r="N93">
-        <v>-12.14687086666667</v>
+        <v>-12.33291706666667</v>
       </c>
       <c r="O93">
-        <v>-3.036717716666667</v>
+        <v>-3.083229266666667</v>
       </c>
       <c r="P93">
-        <v>-9.110153150000002</v>
+        <v>-9.249687800000002</v>
       </c>
       <c r="Q93">
-        <v>-5.680153150000002</v>
+        <v>-5.819687800000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9537322112775258</v>
+        <v>1.067223737687217</v>
       </c>
       <c r="T93">
-        <v>8.780398399658752</v>
+        <v>9.877948199616098</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07063313113100746</v>
+        <v>0.06986537970567042</v>
       </c>
       <c r="W93">
-        <v>0.2191447076793085</v>
+        <v>0.2193257434654029</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2825325245240298</v>
+        <v>0.2794615188226817</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.287157583003148</v>
+        <v>0.289057583003148</v>
       </c>
       <c r="C94">
-        <v>-42.34586453877167</v>
+        <v>-43.37036452470878</v>
       </c>
       <c r="D94">
-        <v>30.15113546122834</v>
+        <v>29.91563547529123</v>
       </c>
       <c r="E94">
-        <v>29.38800000000001</v>
+        <v>30.17700000000001</v>
       </c>
       <c r="F94">
-        <v>72.58800000000001</v>
+        <v>73.37700000000001</v>
       </c>
       <c r="G94">
         <v>0.091</v>
@@ -8995,37 +8995,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M94">
-        <v>17.1162504</v>
+        <v>17.3022966</v>
       </c>
       <c r="N94">
-        <v>-12.33291706666667</v>
+        <v>-12.51896326666667</v>
       </c>
       <c r="O94">
-        <v>-3.083229266666667</v>
+        <v>-3.129740816666667</v>
       </c>
       <c r="P94">
-        <v>-9.249687800000002</v>
+        <v>-9.389222450000002</v>
       </c>
       <c r="Q94">
-        <v>-5.819687800000002</v>
+        <v>-5.959222450000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.067223737687217</v>
+        <v>1.213141414499677</v>
       </c>
       <c r="T94">
-        <v>9.877948199616098</v>
+        <v>11.28908365670411</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06986537970567042</v>
+        <v>0.06911413906367396</v>
       </c>
       <c r="W94">
-        <v>0.2193257434654029</v>
+        <v>0.2195028860087857</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2794615188226817</v>
+        <v>0.2764565562546959</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.289057583003148</v>
+        <v>0.290957583003148</v>
       </c>
       <c r="C95">
-        <v>-43.37036452470878</v>
+        <v>-44.39121420566408</v>
       </c>
       <c r="D95">
-        <v>29.91563547529123</v>
+        <v>29.68378579433593</v>
       </c>
       <c r="E95">
-        <v>30.17700000000001</v>
+        <v>30.96600000000001</v>
       </c>
       <c r="F95">
-        <v>73.37700000000001</v>
+        <v>74.16600000000001</v>
       </c>
       <c r="G95">
         <v>0.091</v>
@@ -9077,37 +9077,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M95">
-        <v>17.3022966</v>
+        <v>17.4883428</v>
       </c>
       <c r="N95">
-        <v>-12.51896326666667</v>
+        <v>-12.70500946666667</v>
       </c>
       <c r="O95">
-        <v>-3.129740816666667</v>
+        <v>-3.176252366666667</v>
       </c>
       <c r="P95">
-        <v>-9.389222450000002</v>
+        <v>-9.528757100000002</v>
       </c>
       <c r="Q95">
-        <v>-5.959222450000002</v>
+        <v>-6.098757100000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.213141414499677</v>
+        <v>1.40769831691629</v>
       </c>
       <c r="T95">
-        <v>11.28908365670411</v>
+        <v>13.17059759948814</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06911413906367396</v>
+        <v>0.06837888226512424</v>
       </c>
       <c r="W95">
-        <v>0.2195028860087857</v>
+        <v>0.2196762595618837</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2764565562546959</v>
+        <v>0.2735155290604969</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.290957583003148</v>
+        <v>0.292857583003148</v>
       </c>
       <c r="C96">
-        <v>-44.39121420566408</v>
+        <v>-45.40849779981113</v>
       </c>
       <c r="D96">
-        <v>29.68378579433593</v>
+        <v>29.45550220018889</v>
       </c>
       <c r="E96">
-        <v>30.96600000000001</v>
+        <v>31.75500000000001</v>
       </c>
       <c r="F96">
-        <v>74.16600000000001</v>
+        <v>74.95500000000001</v>
       </c>
       <c r="G96">
         <v>0.091</v>
@@ -9159,37 +9159,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M96">
-        <v>17.4883428</v>
+        <v>17.67438900000001</v>
       </c>
       <c r="N96">
-        <v>-12.70500946666667</v>
+        <v>-12.89105566666667</v>
       </c>
       <c r="O96">
-        <v>-3.176252366666667</v>
+        <v>-3.222763916666668</v>
       </c>
       <c r="P96">
-        <v>-9.528757100000002</v>
+        <v>-9.668291750000003</v>
       </c>
       <c r="Q96">
-        <v>-6.098757100000002</v>
+        <v>-6.238291750000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.40769831691629</v>
+        <v>1.680077980299548</v>
       </c>
       <c r="T96">
-        <v>13.17059759948814</v>
+        <v>15.80471711938577</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06837888226512424</v>
+        <v>0.06765910455707029</v>
       </c>
       <c r="W96">
-        <v>0.2196762595618837</v>
+        <v>0.2198459831454428</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2735155290604969</v>
+        <v>0.2706364182282811</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.292857583003148</v>
+        <v>0.294757583003148</v>
       </c>
       <c r="C97">
-        <v>-45.40849779981113</v>
+        <v>-46.42229695437092</v>
       </c>
       <c r="D97">
-        <v>29.45550220018889</v>
+        <v>29.2307030456291</v>
       </c>
       <c r="E97">
-        <v>31.75500000000001</v>
+        <v>32.54400000000001</v>
       </c>
       <c r="F97">
-        <v>74.95500000000001</v>
+        <v>75.74400000000001</v>
       </c>
       <c r="G97">
         <v>0.091</v>
@@ -9241,37 +9241,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M97">
-        <v>17.67438900000001</v>
+        <v>17.8604352</v>
       </c>
       <c r="N97">
-        <v>-12.89105566666667</v>
+        <v>-13.07710186666667</v>
       </c>
       <c r="O97">
-        <v>-3.222763916666668</v>
+        <v>-3.269275466666668</v>
       </c>
       <c r="P97">
-        <v>-9.668291750000003</v>
+        <v>-9.807826400000003</v>
       </c>
       <c r="Q97">
-        <v>-6.238291750000004</v>
+        <v>-6.377826400000004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.680077980299548</v>
+        <v>2.088647475374436</v>
       </c>
       <c r="T97">
-        <v>15.80471711938577</v>
+        <v>19.75589639923222</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06765910455707029</v>
+        <v>0.06695432221793414</v>
       </c>
       <c r="W97">
-        <v>0.2198459831454428</v>
+        <v>0.2200121708210111</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2706364182282811</v>
+        <v>0.2678172888717366</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.294757583003148</v>
+        <v>0.296657583003148</v>
       </c>
       <c r="C98">
-        <v>-46.42229695437091</v>
+        <v>-47.43269084297422</v>
       </c>
       <c r="D98">
-        <v>29.2307030456291</v>
+        <v>29.00930915702578</v>
       </c>
       <c r="E98">
-        <v>32.544</v>
+        <v>33.333</v>
       </c>
       <c r="F98">
-        <v>75.744</v>
+        <v>76.533</v>
       </c>
       <c r="G98">
         <v>0.091</v>
@@ -9323,37 +9323,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M98">
-        <v>17.8604352</v>
+        <v>18.0464814</v>
       </c>
       <c r="N98">
-        <v>-13.07710186666667</v>
+        <v>-13.26314806666667</v>
       </c>
       <c r="O98">
-        <v>-3.269275466666667</v>
+        <v>-3.315787016666667</v>
       </c>
       <c r="P98">
-        <v>-9.807826400000001</v>
+        <v>-9.947361050000001</v>
       </c>
       <c r="Q98">
-        <v>-6.377826400000002</v>
+        <v>-6.517361050000002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.088647475374431</v>
+        <v>2.769596633832574</v>
       </c>
       <c r="T98">
-        <v>19.75589639923217</v>
+        <v>26.34119519897623</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06695432221793415</v>
+        <v>0.06626407147341937</v>
       </c>
       <c r="W98">
-        <v>0.2200121708210111</v>
+        <v>0.2201749319465677</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2678172888717366</v>
+        <v>0.2650562858936775</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.296657583003148</v>
+        <v>0.2985575830031479</v>
       </c>
       <c r="C99">
-        <v>-47.43269084297422</v>
+        <v>-48.43975625863244</v>
       </c>
       <c r="D99">
-        <v>29.00930915702578</v>
+        <v>28.79124374136756</v>
       </c>
       <c r="E99">
-        <v>33.333</v>
+        <v>34.122</v>
       </c>
       <c r="F99">
-        <v>76.533</v>
+        <v>77.322</v>
       </c>
       <c r="G99">
         <v>0.091</v>
@@ -9405,37 +9405,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M99">
-        <v>18.0464814</v>
+        <v>18.2325276</v>
       </c>
       <c r="N99">
-        <v>-13.26314806666667</v>
+        <v>-13.44919426666667</v>
       </c>
       <c r="O99">
-        <v>-3.315787016666667</v>
+        <v>-3.362298566666667</v>
       </c>
       <c r="P99">
-        <v>-9.947361050000001</v>
+        <v>-10.0868957</v>
       </c>
       <c r="Q99">
-        <v>-6.517361050000002</v>
+        <v>-6.656895700000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.769596633832574</v>
+        <v>4.131494950748862</v>
       </c>
       <c r="T99">
-        <v>26.34119519897623</v>
+        <v>39.51179279846434</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06626407147341937</v>
+        <v>0.06558790747879265</v>
       </c>
       <c r="W99">
-        <v>0.2201749319465677</v>
+        <v>0.2203343714165007</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2650562858936775</v>
+        <v>0.2623516299151706</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2985575830031479</v>
+        <v>0.300457583003148</v>
       </c>
       <c r="C100">
-        <v>-48.43975625863244</v>
+        <v>-49.44356770254662</v>
       </c>
       <c r="D100">
-        <v>28.79124374136756</v>
+        <v>28.57643229745339</v>
       </c>
       <c r="E100">
-        <v>34.122</v>
+        <v>34.911</v>
       </c>
       <c r="F100">
-        <v>77.322</v>
+        <v>78.111</v>
       </c>
       <c r="G100">
         <v>0.091</v>
@@ -9487,37 +9487,37 @@
         <v>4.783333333333333</v>
       </c>
       <c r="M100">
-        <v>18.2325276</v>
+        <v>18.4185738</v>
       </c>
       <c r="N100">
-        <v>-13.44919426666667</v>
+        <v>-13.63524046666667</v>
       </c>
       <c r="O100">
-        <v>-3.362298566666667</v>
+        <v>-3.408810116666667</v>
       </c>
       <c r="P100">
-        <v>-10.0868957</v>
+        <v>-10.22643035</v>
       </c>
       <c r="Q100">
-        <v>-6.656895700000002</v>
+        <v>-6.796430350000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.131494950748862</v>
+        <v>8.217189901497724</v>
       </c>
       <c r="T100">
-        <v>39.51179279846434</v>
+        <v>79.02358559692868</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06558790747879265</v>
+        <v>0.06492540336284525</v>
       </c>
       <c r="W100">
-        <v>0.2203343714165007</v>
+        <v>0.2204905898870411</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2623516299151706</v>
+        <v>0.259701613451381</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.300457583003148</v>
-      </c>
-      <c r="C101">
-        <v>-49.44356770254662</v>
-      </c>
-      <c r="D101">
-        <v>28.57643229745339</v>
-      </c>
-      <c r="E101">
-        <v>34.911</v>
-      </c>
-      <c r="F101">
-        <v>78.111</v>
-      </c>
-      <c r="G101">
-        <v>0.091</v>
-      </c>
-      <c r="H101">
-        <v>35.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.213333333333333</v>
-      </c>
-      <c r="K101">
-        <v>3.43</v>
-      </c>
-      <c r="L101">
-        <v>4.783333333333333</v>
-      </c>
-      <c r="M101">
-        <v>18.4185738</v>
-      </c>
-      <c r="N101">
-        <v>-13.63524046666667</v>
-      </c>
-      <c r="O101">
-        <v>-3.408810116666667</v>
-      </c>
-      <c r="P101">
-        <v>-10.22643035</v>
-      </c>
-      <c r="Q101">
-        <v>-6.796430350000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.217189901497724</v>
-      </c>
-      <c r="T101">
-        <v>79.02358559692868</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06492540336284525</v>
-      </c>
-      <c r="W101">
-        <v>0.2204905898870411</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.259701613451381</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
